--- a/PROPERTIES/MONICA/MONICA2025.xlsx
+++ b/PROPERTIES/MONICA/MONICA2025.xlsx
@@ -10,7 +10,7 @@
   <sheets>
     <sheet name="JUNE" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="JULY" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="JULY2" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="AUG" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="663" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="223">
   <si>
     <t xml:space="preserve">HOUSE NO</t>
   </si>
@@ -685,6 +685,9 @@
   </si>
   <si>
     <t xml:space="preserve">NO TEXT YET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">get name???</t>
   </si>
   <si>
     <t xml:space="preserve">PHOEBE</t>
@@ -700,7 +703,7 @@
     <numFmt numFmtId="166" formatCode="#,##0.00"/>
     <numFmt numFmtId="167" formatCode="#,##0"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -836,8 +839,8 @@
     </font>
     <font>
       <b val="true"/>
-      <u val="single"/>
-      <sz val="12"/>
+      <sz val="10.5"/>
+      <color rgb="FF000000"/>
       <name val="Georgia"/>
       <family val="1"/>
     </font>
@@ -848,13 +851,7 @@
       <color rgb="FF000000"/>
       <name val="Georgia"/>
       <family val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="13">
@@ -986,7 +983,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="78">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1291,15 +1288,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="19" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="20" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -7493,9 +7486,7 @@
       <c r="D3" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E3" s="13" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E3" s="13"/>
       <c r="F3" s="13"/>
     </row>
     <row r="4" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7511,9 +7502,7 @@
       <c r="D4" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E4" s="13" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E4" s="13"/>
       <c r="F4" s="13"/>
     </row>
     <row r="5" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7529,9 +7518,7 @@
       <c r="D5" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E5" s="14" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E5" s="14"/>
       <c r="F5" s="14"/>
     </row>
     <row r="6" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7547,9 +7534,7 @@
       <c r="D6" s="12" t="n">
         <v>8500</v>
       </c>
-      <c r="E6" s="14" t="n">
-        <v>8500</v>
-      </c>
+      <c r="E6" s="14"/>
       <c r="F6" s="14"/>
     </row>
     <row r="7" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7565,9 +7550,7 @@
       <c r="D7" s="18" t="n">
         <v>5000</v>
       </c>
-      <c r="E7" s="19" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E7" s="19"/>
       <c r="F7" s="19"/>
     </row>
     <row r="8" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7583,9 +7566,7 @@
       <c r="D8" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E8" s="20" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E8" s="20"/>
       <c r="F8" s="20"/>
     </row>
     <row r="9" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7601,9 +7582,7 @@
       <c r="D9" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E9" s="20" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E9" s="20"/>
       <c r="F9" s="20"/>
     </row>
     <row r="10" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7619,9 +7598,7 @@
       <c r="D10" s="18" t="n">
         <v>5000</v>
       </c>
-      <c r="E10" s="21" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E10" s="21"/>
       <c r="F10" s="21"/>
     </row>
     <row r="11" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7637,9 +7614,7 @@
       <c r="D11" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E11" s="20" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E11" s="20"/>
       <c r="F11" s="20"/>
     </row>
     <row r="12" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7655,9 +7630,7 @@
       <c r="D12" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E12" s="14" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E12" s="14"/>
       <c r="F12" s="14"/>
     </row>
     <row r="13" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7673,9 +7646,7 @@
       <c r="D13" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E13" s="14" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E13" s="14"/>
       <c r="F13" s="14"/>
     </row>
     <row r="14" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7689,9 +7660,7 @@
       <c r="D14" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E14" s="20" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E14" s="20"/>
       <c r="F14" s="20"/>
     </row>
     <row r="15" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7707,9 +7676,7 @@
       <c r="D15" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E15" s="20" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E15" s="20"/>
       <c r="F15" s="20"/>
     </row>
     <row r="16" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7725,9 +7692,7 @@
       <c r="D16" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E16" s="20" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E16" s="20"/>
       <c r="F16" s="20"/>
     </row>
     <row r="17" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7739,9 +7704,7 @@
       <c r="D17" s="18" t="n">
         <v>5000</v>
       </c>
-      <c r="E17" s="19" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E17" s="19"/>
       <c r="F17" s="19"/>
     </row>
     <row r="18" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7757,9 +7720,7 @@
       <c r="D18" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E18" s="14" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E18" s="14"/>
       <c r="F18" s="14"/>
     </row>
     <row r="19" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7775,9 +7736,7 @@
       <c r="D19" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E19" s="14" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E19" s="14"/>
       <c r="F19" s="14"/>
     </row>
     <row r="20" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7793,9 +7752,7 @@
       <c r="D20" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E20" s="14" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E20" s="14"/>
       <c r="F20" s="14"/>
     </row>
     <row r="21" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7811,9 +7768,7 @@
       <c r="D21" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E21" s="20" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E21" s="20"/>
       <c r="F21" s="20"/>
     </row>
     <row r="22" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7829,9 +7784,7 @@
       <c r="D22" s="18" t="n">
         <v>5000</v>
       </c>
-      <c r="E22" s="19" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E22" s="19"/>
       <c r="F22" s="19"/>
     </row>
     <row r="23" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7847,9 +7800,7 @@
       <c r="D23" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E23" s="14" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E23" s="14"/>
       <c r="F23" s="14"/>
     </row>
     <row r="24" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7865,9 +7816,7 @@
       <c r="D24" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E24" s="20" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E24" s="20"/>
       <c r="F24" s="20"/>
     </row>
     <row r="25" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7883,9 +7832,7 @@
       <c r="D25" s="12" t="n">
         <v>6000</v>
       </c>
-      <c r="E25" s="20" t="n">
-        <v>6000</v>
-      </c>
+      <c r="E25" s="20"/>
       <c r="F25" s="20"/>
     </row>
     <row r="26" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7901,9 +7848,7 @@
       <c r="D26" s="18" t="n">
         <v>6000</v>
       </c>
-      <c r="E26" s="19" t="n">
-        <v>6000</v>
-      </c>
+      <c r="E26" s="19"/>
       <c r="F26" s="19"/>
     </row>
     <row r="27" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7919,9 +7864,7 @@
       <c r="D27" s="12" t="n">
         <v>6000</v>
       </c>
-      <c r="E27" s="14" t="n">
-        <v>6000</v>
-      </c>
+      <c r="E27" s="14"/>
       <c r="F27" s="14"/>
     </row>
     <row r="28" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7937,9 +7880,7 @@
       <c r="D28" s="18" t="n">
         <v>6000</v>
       </c>
-      <c r="E28" s="19" t="n">
-        <v>6000</v>
-      </c>
+      <c r="E28" s="19"/>
       <c r="F28" s="19"/>
     </row>
     <row r="29" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7955,9 +7896,7 @@
       <c r="D29" s="12" t="n">
         <v>6000</v>
       </c>
-      <c r="E29" s="14" t="n">
-        <v>6000</v>
-      </c>
+      <c r="E29" s="14"/>
       <c r="F29" s="14"/>
     </row>
     <row r="30" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7973,9 +7912,7 @@
       <c r="D30" s="12" t="n">
         <v>6000</v>
       </c>
-      <c r="E30" s="14" t="n">
-        <v>6000</v>
-      </c>
+      <c r="E30" s="14"/>
       <c r="F30" s="14"/>
     </row>
     <row r="31" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7991,9 +7928,7 @@
       <c r="D31" s="12" t="n">
         <v>6000</v>
       </c>
-      <c r="E31" s="14" t="n">
-        <v>6000</v>
-      </c>
+      <c r="E31" s="14"/>
       <c r="F31" s="14"/>
     </row>
     <row r="32" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8009,9 +7944,7 @@
       <c r="D32" s="26" t="n">
         <v>6000</v>
       </c>
-      <c r="E32" s="27" t="n">
-        <v>6000</v>
-      </c>
+      <c r="E32" s="27"/>
       <c r="F32" s="27"/>
     </row>
     <row r="33" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8027,9 +7960,7 @@
       <c r="D33" s="31" t="n">
         <v>6000</v>
       </c>
-      <c r="E33" s="32" t="n">
-        <v>6000</v>
-      </c>
+      <c r="E33" s="32"/>
       <c r="F33" s="20"/>
     </row>
     <row r="34" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8045,9 +7976,7 @@
       <c r="D34" s="12" t="n">
         <v>6000</v>
       </c>
-      <c r="E34" s="14" t="n">
-        <v>6000</v>
-      </c>
+      <c r="E34" s="14"/>
       <c r="F34" s="14"/>
     </row>
     <row r="35" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8060,10 +7989,7 @@
         <f aca="false">SUM(D3:D34)</f>
         <v>173500</v>
       </c>
-      <c r="E35" s="34" t="n">
-        <f aca="false">SUM(E3:E34)</f>
-        <v>173500</v>
-      </c>
+      <c r="E35" s="34"/>
       <c r="F35" s="1"/>
     </row>
     <row r="36" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8095,9 +8021,7 @@
       <c r="D38" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E38" s="71" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E38" s="71"/>
       <c r="F38" s="1"/>
     </row>
     <row r="39" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8113,9 +8037,7 @@
       <c r="D39" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E39" s="71" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E39" s="71"/>
       <c r="F39" s="1"/>
     </row>
     <row r="40" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8131,9 +8053,7 @@
       <c r="D40" s="26" t="n">
         <v>5000</v>
       </c>
-      <c r="E40" s="38" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E40" s="38"/>
       <c r="F40" s="1"/>
     </row>
     <row r="41" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8149,9 +8069,7 @@
       <c r="D41" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E41" s="14" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E41" s="14"/>
       <c r="F41" s="1"/>
     </row>
     <row r="42" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8167,9 +8085,7 @@
       <c r="D42" s="18" t="n">
         <v>5000</v>
       </c>
-      <c r="E42" s="71" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E42" s="71"/>
       <c r="F42" s="1"/>
     </row>
     <row r="43" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8185,9 +8101,7 @@
       <c r="D43" s="40" t="n">
         <v>8500</v>
       </c>
-      <c r="E43" s="41" t="n">
-        <v>8500</v>
-      </c>
+      <c r="E43" s="41"/>
       <c r="F43" s="1"/>
     </row>
     <row r="44" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8201,9 +8115,7 @@
       <c r="D44" s="45" t="n">
         <v>5000</v>
       </c>
-      <c r="E44" s="72" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E44" s="72"/>
       <c r="F44" s="1"/>
     </row>
     <row r="45" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8219,9 +8131,7 @@
       <c r="D45" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E45" s="14" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E45" s="14"/>
       <c r="F45" s="1"/>
     </row>
     <row r="46" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8237,9 +8147,7 @@
       <c r="D46" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E46" s="14" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E46" s="14"/>
       <c r="F46" s="1"/>
     </row>
     <row r="47" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8252,10 +8160,7 @@
         <f aca="false">SUM(D38:D46)</f>
         <v>48500</v>
       </c>
-      <c r="E47" s="49" t="n">
-        <f aca="false">SUM(E38:E46)</f>
-        <v>48500</v>
-      </c>
+      <c r="E47" s="49"/>
       <c r="F47" s="1"/>
     </row>
     <row r="48" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8308,9 +8213,7 @@
       <c r="D53" s="12" t="n">
         <v>8500</v>
       </c>
-      <c r="E53" s="20" t="n">
-        <v>8500</v>
-      </c>
+      <c r="E53" s="20"/>
       <c r="F53" s="1"/>
     </row>
     <row r="54" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8326,9 +8229,7 @@
       <c r="D54" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E54" s="14" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E54" s="14"/>
       <c r="F54" s="1"/>
     </row>
     <row r="55" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8344,9 +8245,7 @@
       <c r="D55" s="18" t="n">
         <v>5000</v>
       </c>
-      <c r="E55" s="21" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E55" s="21"/>
       <c r="F55" s="1"/>
     </row>
     <row r="56" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8362,9 +8261,7 @@
       <c r="D56" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E56" s="71" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E56" s="71"/>
       <c r="F56" s="1"/>
     </row>
     <row r="57" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8380,9 +8277,7 @@
       <c r="D57" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E57" s="71" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E57" s="71"/>
       <c r="F57" s="1"/>
     </row>
     <row r="58" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8398,9 +8293,7 @@
       <c r="D58" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E58" s="14" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E58" s="14"/>
       <c r="F58" s="1"/>
     </row>
     <row r="59" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8416,9 +8309,7 @@
       <c r="D59" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E59" s="71" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E59" s="71"/>
       <c r="F59" s="1"/>
     </row>
     <row r="60" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8434,9 +8325,7 @@
       <c r="D60" s="18" t="n">
         <v>8500</v>
       </c>
-      <c r="E60" s="19" t="n">
-        <v>8500</v>
-      </c>
+      <c r="E60" s="19"/>
       <c r="F60" s="1"/>
     </row>
     <row r="61" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8449,10 +8338,7 @@
         <f aca="false">SUM(D53:D60)</f>
         <v>47000</v>
       </c>
-      <c r="E61" s="50" t="n">
-        <f aca="false">SUM(E53:E60)</f>
-        <v>47000</v>
-      </c>
+      <c r="E61" s="50"/>
       <c r="F61" s="1"/>
     </row>
     <row r="62" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8491,9 +8377,7 @@
       <c r="D65" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E65" s="71" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E65" s="71"/>
       <c r="F65" s="1"/>
     </row>
     <row r="66" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8509,9 +8393,7 @@
       <c r="D66" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E66" s="71" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E66" s="71"/>
       <c r="F66" s="1"/>
     </row>
     <row r="67" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8527,9 +8409,7 @@
       <c r="D67" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E67" s="73" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E67" s="73"/>
       <c r="F67" s="1"/>
     </row>
     <row r="68" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8545,9 +8425,7 @@
       <c r="D68" s="12" t="n">
         <v>8500</v>
       </c>
-      <c r="E68" s="20" t="n">
-        <v>8500</v>
-      </c>
+      <c r="E68" s="20"/>
       <c r="F68" s="1"/>
     </row>
     <row r="69" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8563,9 +8441,7 @@
       <c r="D69" s="12" t="n">
         <v>8500</v>
       </c>
-      <c r="E69" s="20" t="n">
-        <v>8500</v>
-      </c>
+      <c r="E69" s="20"/>
       <c r="F69" s="1"/>
     </row>
     <row r="70" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8581,9 +8457,7 @@
       <c r="D70" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E70" s="14" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E70" s="14"/>
       <c r="F70" s="1"/>
     </row>
     <row r="71" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8599,9 +8473,7 @@
       <c r="D71" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E71" s="14" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E71" s="14"/>
       <c r="F71" s="1"/>
     </row>
     <row r="72" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8617,9 +8489,7 @@
       <c r="D72" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E72" s="71" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E72" s="71"/>
       <c r="F72" s="1"/>
     </row>
     <row r="73" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8653,9 +8523,7 @@
       <c r="D74" s="18" t="n">
         <v>5000</v>
       </c>
-      <c r="E74" s="21" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E74" s="21"/>
       <c r="F74" s="1"/>
     </row>
     <row r="75" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8671,9 +8539,7 @@
       <c r="D75" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E75" s="20" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E75" s="20"/>
       <c r="F75" s="1"/>
     </row>
     <row r="76" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8689,9 +8555,7 @@
       <c r="D76" s="26" t="n">
         <v>5000</v>
       </c>
-      <c r="E76" s="75" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E76" s="75"/>
       <c r="F76" s="1"/>
     </row>
     <row r="77" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8707,9 +8571,7 @@
       <c r="D77" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E77" s="71" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E77" s="71"/>
       <c r="F77" s="1"/>
     </row>
     <row r="78" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8725,19 +8587,21 @@
       <c r="D78" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E78" s="71" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E78" s="71"/>
       <c r="F78" s="1"/>
     </row>
     <row r="79" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="23" t="n">
         <v>15</v>
       </c>
-      <c r="B79" s="24"/>
+      <c r="B79" s="24" t="s">
+        <v>221</v>
+      </c>
       <c r="C79" s="25"/>
       <c r="D79" s="26"/>
-      <c r="E79" s="75"/>
+      <c r="E79" s="75" t="n">
+        <v>5000</v>
+      </c>
       <c r="F79" s="1"/>
     </row>
     <row r="80" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8765,9 +8629,7 @@
       <c r="D81" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E81" s="71" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E81" s="71"/>
       <c r="F81" s="1"/>
     </row>
     <row r="82" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8783,9 +8645,7 @@
       <c r="D82" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E82" s="14" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E82" s="14"/>
       <c r="F82" s="1"/>
     </row>
     <row r="83" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8801,9 +8661,7 @@
       <c r="D83" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E83" s="71" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E83" s="71"/>
       <c r="F83" s="1"/>
     </row>
     <row r="84" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8819,9 +8677,7 @@
       <c r="D84" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E84" s="20" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E84" s="20"/>
       <c r="F84" s="1"/>
     </row>
     <row r="85" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8837,9 +8693,7 @@
       <c r="D85" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E85" s="14" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E85" s="14"/>
       <c r="F85" s="1"/>
     </row>
     <row r="86" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8855,9 +8709,7 @@
       <c r="D86" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E86" s="71" t="n">
-        <v>5000</v>
-      </c>
+      <c r="E86" s="71"/>
       <c r="F86" s="1"/>
     </row>
     <row r="87" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8870,10 +8722,7 @@
         <f aca="false">SUM(D65:D86)</f>
         <v>107000</v>
       </c>
-      <c r="E87" s="51" t="n">
-        <f aca="false">SUM(E65:E86)</f>
-        <v>107000</v>
-      </c>
+      <c r="E87" s="51"/>
       <c r="F87" s="1"/>
     </row>
     <row r="88" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8948,9 +8797,7 @@
       <c r="D93" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E93" s="20" t="n">
-        <v>11000</v>
-      </c>
+      <c r="E93" s="20"/>
       <c r="F93" s="1"/>
     </row>
     <row r="94" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8966,9 +8813,7 @@
       <c r="D94" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E94" s="14" t="n">
-        <v>11000</v>
-      </c>
+      <c r="E94" s="14"/>
       <c r="F94" s="1"/>
     </row>
     <row r="95" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8984,9 +8829,7 @@
       <c r="D95" s="26" t="n">
         <v>11000</v>
       </c>
-      <c r="E95" s="38" t="n">
-        <v>11000</v>
-      </c>
+      <c r="E95" s="38"/>
       <c r="F95" s="1"/>
     </row>
     <row r="96" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9000,9 +8843,7 @@
       <c r="D96" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E96" s="20" t="n">
-        <v>11000</v>
-      </c>
+      <c r="E96" s="20"/>
       <c r="F96" s="1"/>
     </row>
     <row r="97" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9018,9 +8859,7 @@
       <c r="D97" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E97" s="14" t="n">
-        <v>11000</v>
-      </c>
+      <c r="E97" s="14"/>
       <c r="F97" s="1"/>
     </row>
     <row r="98" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9036,9 +8875,7 @@
       <c r="D98" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E98" s="20" t="n">
-        <v>11000</v>
-      </c>
+      <c r="E98" s="20"/>
       <c r="F98" s="1"/>
     </row>
     <row r="99" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9054,9 +8891,7 @@
       <c r="D99" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E99" s="14" t="n">
-        <v>11000</v>
-      </c>
+      <c r="E99" s="14"/>
       <c r="F99" s="1"/>
     </row>
     <row r="100" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9072,9 +8907,7 @@
       <c r="D100" s="12" t="n">
         <v>13000</v>
       </c>
-      <c r="E100" s="20" t="n">
-        <v>13000</v>
-      </c>
+      <c r="E100" s="20"/>
       <c r="F100" s="1"/>
     </row>
     <row r="101" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9090,9 +8923,7 @@
       <c r="D101" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E101" s="14" t="n">
-        <v>11000</v>
-      </c>
+      <c r="E101" s="14"/>
       <c r="F101" s="1"/>
     </row>
     <row r="102" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9108,9 +8939,7 @@
       <c r="D102" s="53" t="n">
         <v>10000</v>
       </c>
-      <c r="E102" s="14" t="n">
-        <v>10000</v>
-      </c>
+      <c r="E102" s="14"/>
       <c r="F102" s="1"/>
     </row>
     <row r="103" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9126,9 +8955,7 @@
       <c r="D103" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E103" s="20" t="n">
-        <v>11000</v>
-      </c>
+      <c r="E103" s="20"/>
       <c r="F103" s="1"/>
     </row>
     <row r="104" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9144,9 +8971,7 @@
       <c r="D104" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E104" s="14" t="n">
-        <v>11000</v>
-      </c>
+      <c r="E104" s="14"/>
       <c r="F104" s="1"/>
     </row>
     <row r="105" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9159,10 +8984,7 @@
         <f aca="false">SUM(D91:D104)</f>
         <v>154000</v>
       </c>
-      <c r="E105" s="51" t="n">
-        <f aca="false">SUM(E91:E104)</f>
-        <v>154000</v>
-      </c>
+      <c r="E105" s="51"/>
       <c r="F105" s="1"/>
     </row>
     <row r="106" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9208,9 +9030,7 @@
       <c r="D110" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E110" s="14" t="n">
-        <v>11000</v>
-      </c>
+      <c r="E110" s="14"/>
       <c r="F110" s="1"/>
     </row>
     <row r="111" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9226,9 +9046,7 @@
       <c r="D111" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E111" s="14" t="n">
-        <v>11000</v>
-      </c>
+      <c r="E111" s="14"/>
       <c r="F111" s="1"/>
     </row>
     <row r="112" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9244,9 +9062,7 @@
       <c r="D112" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E112" s="20" t="n">
-        <v>11000</v>
-      </c>
+      <c r="E112" s="20"/>
       <c r="F112" s="1"/>
     </row>
     <row r="113" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9262,9 +9078,7 @@
       <c r="D113" s="12" t="n">
         <v>14000</v>
       </c>
-      <c r="E113" s="20" t="n">
-        <v>14000</v>
-      </c>
+      <c r="E113" s="20"/>
       <c r="F113" s="1"/>
     </row>
     <row r="114" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9280,9 +9094,7 @@
       <c r="D114" s="26" t="n">
         <v>11000</v>
       </c>
-      <c r="E114" s="27" t="n">
-        <v>11000</v>
-      </c>
+      <c r="E114" s="27"/>
       <c r="F114" s="1"/>
     </row>
     <row r="115" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9298,9 +9110,7 @@
       <c r="D115" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E115" s="14" t="n">
-        <v>11000</v>
-      </c>
+      <c r="E115" s="14"/>
       <c r="F115" s="1"/>
     </row>
     <row r="116" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9316,9 +9126,7 @@
       <c r="D116" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E116" s="20" t="n">
-        <v>11000</v>
-      </c>
+      <c r="E116" s="20"/>
       <c r="F116" s="1"/>
     </row>
     <row r="117" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9334,9 +9142,7 @@
       <c r="D117" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E117" s="14" t="n">
-        <v>11000</v>
-      </c>
+      <c r="E117" s="14"/>
       <c r="F117" s="1"/>
     </row>
     <row r="118" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9352,9 +9158,7 @@
       <c r="D118" s="18" t="n">
         <v>14000</v>
       </c>
-      <c r="E118" s="21" t="n">
-        <v>14000</v>
-      </c>
+      <c r="E118" s="21"/>
       <c r="F118" s="1"/>
     </row>
     <row r="119" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9370,9 +9174,7 @@
       <c r="D119" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E119" s="20" t="n">
-        <v>11000</v>
-      </c>
+      <c r="E119" s="20"/>
       <c r="F119" s="1"/>
     </row>
     <row r="120" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9388,9 +9190,7 @@
       <c r="D120" s="18" t="n">
         <v>11000</v>
       </c>
-      <c r="E120" s="19" t="n">
-        <v>11000</v>
-      </c>
+      <c r="E120" s="19"/>
       <c r="F120" s="1"/>
     </row>
     <row r="121" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9424,9 +9224,7 @@
       <c r="D122" s="18" t="n">
         <v>11000</v>
       </c>
-      <c r="E122" s="19" t="n">
-        <v>11000</v>
-      </c>
+      <c r="E122" s="19"/>
       <c r="F122" s="1"/>
     </row>
     <row r="123" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9442,9 +9240,7 @@
       <c r="D123" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E123" s="14" t="n">
-        <v>11000</v>
-      </c>
+      <c r="E123" s="14"/>
       <c r="F123" s="55"/>
     </row>
     <row r="124" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9452,7 +9248,7 @@
         <v>15</v>
       </c>
       <c r="B124" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C124" s="11" t="n">
         <v>740808927</v>
@@ -9460,9 +9256,7 @@
       <c r="D124" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E124" s="20" t="n">
-        <v>11000</v>
-      </c>
+      <c r="E124" s="20"/>
       <c r="F124" s="1"/>
     </row>
     <row r="125" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9478,9 +9272,7 @@
       <c r="D125" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E125" s="20" t="n">
-        <v>11000</v>
-      </c>
+      <c r="E125" s="20"/>
       <c r="F125" s="1"/>
     </row>
     <row r="126" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9496,9 +9288,7 @@
       <c r="D126" s="12" t="n">
         <v>14000</v>
       </c>
-      <c r="E126" s="20" t="n">
-        <v>14000</v>
-      </c>
+      <c r="E126" s="20"/>
       <c r="F126" s="1"/>
     </row>
     <row r="127" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9514,9 +9304,7 @@
       <c r="D127" s="18" t="n">
         <v>11000</v>
       </c>
-      <c r="E127" s="21" t="n">
-        <v>11000</v>
-      </c>
+      <c r="E127" s="21"/>
       <c r="F127" s="1"/>
     </row>
     <row r="128" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9532,9 +9320,7 @@
       <c r="D128" s="18" t="n">
         <v>11000</v>
       </c>
-      <c r="E128" s="21" t="n">
-        <v>11000</v>
-      </c>
+      <c r="E128" s="21"/>
       <c r="F128" s="1"/>
     </row>
     <row r="129" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9550,9 +9336,7 @@
       <c r="D129" s="18" t="n">
         <v>11000</v>
       </c>
-      <c r="E129" s="19" t="n">
-        <v>11000</v>
-      </c>
+      <c r="E129" s="19"/>
       <c r="F129" s="1"/>
     </row>
     <row r="130" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9568,9 +9352,7 @@
       <c r="D130" s="12" t="n">
         <v>16000</v>
       </c>
-      <c r="E130" s="14" t="n">
-        <v>16000</v>
-      </c>
+      <c r="E130" s="14"/>
       <c r="F130" s="1"/>
     </row>
     <row r="131" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9583,9 +9365,9 @@
         <f aca="false">SUM(D110:D130)</f>
         <v>245000</v>
       </c>
-      <c r="E131" s="57" t="n">
-        <f aca="false">SUM(E110:E130)</f>
-        <v>245000</v>
+      <c r="E131" s="76" t="n">
+        <f aca="false">SUM(E3:E129)</f>
+        <v>42000</v>
       </c>
       <c r="F131" s="1"/>
     </row>
@@ -9609,7 +9391,7 @@
       <c r="C134" s="59" t="s">
         <v>211</v>
       </c>
-      <c r="D134" s="76" t="n">
+      <c r="D134" s="69" t="n">
         <v>775000</v>
       </c>
       <c r="E134" s="77" t="n">
@@ -9630,7 +9412,7 @@
       <c r="C136" s="59" t="s">
         <v>212</v>
       </c>
-      <c r="E136" s="78" t="n">
+      <c r="E136" s="63" t="n">
         <v>38750</v>
       </c>
       <c r="F136" s="61"/>
@@ -9648,7 +9430,7 @@
       <c r="C138" s="59" t="s">
         <v>213</v>
       </c>
-      <c r="E138" s="78" t="n">
+      <c r="E138" s="63" t="n">
         <v>736250</v>
       </c>
       <c r="F138" s="61"/>

--- a/PROPERTIES/MONICA/MONICA2025.xlsx
+++ b/PROPERTIES/MONICA/MONICA2025.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="225">
   <si>
     <t xml:space="preserve">HOUSE NO</t>
   </si>
@@ -685,6 +685,12 @@
   </si>
   <si>
     <t xml:space="preserve">NO TEXT YET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">????</t>
   </si>
   <si>
     <t xml:space="preserve">get name???</t>
@@ -703,7 +709,7 @@
     <numFmt numFmtId="166" formatCode="#,##0.00"/>
     <numFmt numFmtId="167" formatCode="#,##0"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -840,9 +846,19 @@
     <font>
       <b val="true"/>
       <sz val="10.5"/>
-      <color rgb="FF000000"/>
+      <color rgb="FF008000"/>
       <name val="Georgia"/>
       <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <u val="single"/>
+      <sz val="10.5"/>
+      <color rgb="FF008000"/>
+      <name val="Georgia"/>
+      <family val="1"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -924,7 +940,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF228B22"/>
-        <bgColor rgb="FF00A933"/>
+        <bgColor rgb="FF008000"/>
       </patternFill>
     </fill>
   </fills>
@@ -983,7 +999,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="87">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1268,31 +1284,67 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="11" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="19" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="19" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="19" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="19" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="20" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="11" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1316,11 +1368,11 @@
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF228B22"/>
+      <rgbColor rgb="FF008000"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF00A933"/>
       <rgbColor rgb="FFB3CAC7"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
@@ -1356,7 +1408,7 @@
       <rgbColor rgb="FF666699"/>
       <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF00A933"/>
+      <rgbColor rgb="FF228B22"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FF993300"/>
@@ -7455,7 +7507,7 @@
         <v>2</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="F1" s="6"/>
     </row>
@@ -7486,7 +7538,7 @@
       <c r="D3" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E3" s="13"/>
+      <c r="E3" s="71"/>
       <c r="F3" s="13"/>
     </row>
     <row r="4" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7502,7 +7554,9 @@
       <c r="D4" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E4" s="13"/>
+      <c r="E4" s="71" t="n">
+        <v>5000</v>
+      </c>
       <c r="F4" s="13"/>
     </row>
     <row r="5" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7518,7 +7572,9 @@
       <c r="D5" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E5" s="14"/>
+      <c r="E5" s="72" t="n">
+        <v>5000</v>
+      </c>
       <c r="F5" s="14"/>
     </row>
     <row r="6" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7534,7 +7590,7 @@
       <c r="D6" s="12" t="n">
         <v>8500</v>
       </c>
-      <c r="E6" s="14"/>
+      <c r="E6" s="72"/>
       <c r="F6" s="14"/>
     </row>
     <row r="7" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7550,7 +7606,7 @@
       <c r="D7" s="18" t="n">
         <v>5000</v>
       </c>
-      <c r="E7" s="19"/>
+      <c r="E7" s="73"/>
       <c r="F7" s="19"/>
     </row>
     <row r="8" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7566,7 +7622,9 @@
       <c r="D8" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E8" s="20"/>
+      <c r="E8" s="74" t="n">
+        <v>5000</v>
+      </c>
       <c r="F8" s="20"/>
     </row>
     <row r="9" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7574,15 +7632,15 @@
         <v>7</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>20</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="C9" s="11"/>
       <c r="D9" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E9" s="20"/>
+      <c r="E9" s="74" t="n">
+        <v>5000</v>
+      </c>
       <c r="F9" s="20"/>
     </row>
     <row r="10" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7598,7 +7656,7 @@
       <c r="D10" s="18" t="n">
         <v>5000</v>
       </c>
-      <c r="E10" s="21"/>
+      <c r="E10" s="75"/>
       <c r="F10" s="21"/>
     </row>
     <row r="11" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7614,7 +7672,7 @@
       <c r="D11" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E11" s="20"/>
+      <c r="E11" s="74"/>
       <c r="F11" s="20"/>
     </row>
     <row r="12" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7624,13 +7682,15 @@
       <c r="B12" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="11" t="s">
-        <v>10</v>
+      <c r="C12" s="11" t="n">
+        <v>729275621</v>
       </c>
       <c r="D12" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E12" s="14"/>
+      <c r="E12" s="72" t="n">
+        <v>5000</v>
+      </c>
       <c r="F12" s="14"/>
     </row>
     <row r="13" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7646,7 +7706,9 @@
       <c r="D13" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E13" s="14"/>
+      <c r="E13" s="72" t="n">
+        <v>5000</v>
+      </c>
       <c r="F13" s="14"/>
     </row>
     <row r="14" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7660,7 +7722,7 @@
       <c r="D14" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E14" s="20"/>
+      <c r="E14" s="74"/>
       <c r="F14" s="20"/>
     </row>
     <row r="15" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7676,7 +7738,7 @@
       <c r="D15" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E15" s="20"/>
+      <c r="E15" s="74"/>
       <c r="F15" s="20"/>
     </row>
     <row r="16" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7692,7 +7754,7 @@
       <c r="D16" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E16" s="20"/>
+      <c r="E16" s="74"/>
       <c r="F16" s="20"/>
     </row>
     <row r="17" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7704,7 +7766,7 @@
       <c r="D17" s="18" t="n">
         <v>5000</v>
       </c>
-      <c r="E17" s="19"/>
+      <c r="E17" s="73"/>
       <c r="F17" s="19"/>
     </row>
     <row r="18" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7720,7 +7782,9 @@
       <c r="D18" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E18" s="14"/>
+      <c r="E18" s="72" t="n">
+        <v>5000</v>
+      </c>
       <c r="F18" s="14"/>
     </row>
     <row r="19" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7736,7 +7800,9 @@
       <c r="D19" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E19" s="14"/>
+      <c r="E19" s="72" t="n">
+        <v>5000</v>
+      </c>
       <c r="F19" s="14"/>
     </row>
     <row r="20" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7752,7 +7818,9 @@
       <c r="D20" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E20" s="14"/>
+      <c r="E20" s="72" t="n">
+        <v>5000</v>
+      </c>
       <c r="F20" s="14"/>
     </row>
     <row r="21" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7768,7 +7836,7 @@
       <c r="D21" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E21" s="20"/>
+      <c r="E21" s="74"/>
       <c r="F21" s="20"/>
     </row>
     <row r="22" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7784,7 +7852,7 @@
       <c r="D22" s="18" t="n">
         <v>5000</v>
       </c>
-      <c r="E22" s="19"/>
+      <c r="E22" s="73"/>
       <c r="F22" s="19"/>
     </row>
     <row r="23" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7800,7 +7868,9 @@
       <c r="D23" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E23" s="14"/>
+      <c r="E23" s="72" t="n">
+        <v>5000</v>
+      </c>
       <c r="F23" s="14"/>
     </row>
     <row r="24" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7816,7 +7886,7 @@
       <c r="D24" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E24" s="20"/>
+      <c r="E24" s="74"/>
       <c r="F24" s="20"/>
     </row>
     <row r="25" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7832,7 +7902,9 @@
       <c r="D25" s="12" t="n">
         <v>6000</v>
       </c>
-      <c r="E25" s="20"/>
+      <c r="E25" s="74" t="n">
+        <v>6000</v>
+      </c>
       <c r="F25" s="20"/>
     </row>
     <row r="26" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7848,7 +7920,7 @@
       <c r="D26" s="18" t="n">
         <v>6000</v>
       </c>
-      <c r="E26" s="19"/>
+      <c r="E26" s="73"/>
       <c r="F26" s="19"/>
     </row>
     <row r="27" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7864,7 +7936,9 @@
       <c r="D27" s="12" t="n">
         <v>6000</v>
       </c>
-      <c r="E27" s="14"/>
+      <c r="E27" s="72" t="n">
+        <v>6000</v>
+      </c>
       <c r="F27" s="14"/>
     </row>
     <row r="28" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7880,7 +7954,7 @@
       <c r="D28" s="18" t="n">
         <v>6000</v>
       </c>
-      <c r="E28" s="19"/>
+      <c r="E28" s="73"/>
       <c r="F28" s="19"/>
     </row>
     <row r="29" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7896,7 +7970,9 @@
       <c r="D29" s="12" t="n">
         <v>6000</v>
       </c>
-      <c r="E29" s="14"/>
+      <c r="E29" s="72" t="n">
+        <v>6000</v>
+      </c>
       <c r="F29" s="14"/>
     </row>
     <row r="30" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7912,7 +7988,7 @@
       <c r="D30" s="12" t="n">
         <v>6000</v>
       </c>
-      <c r="E30" s="14"/>
+      <c r="E30" s="72"/>
       <c r="F30" s="14"/>
     </row>
     <row r="31" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7928,7 +8004,7 @@
       <c r="D31" s="12" t="n">
         <v>6000</v>
       </c>
-      <c r="E31" s="14"/>
+      <c r="E31" s="72"/>
       <c r="F31" s="14"/>
     </row>
     <row r="32" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7944,7 +8020,7 @@
       <c r="D32" s="26" t="n">
         <v>6000</v>
       </c>
-      <c r="E32" s="27"/>
+      <c r="E32" s="76"/>
       <c r="F32" s="27"/>
     </row>
     <row r="33" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7960,7 +8036,9 @@
       <c r="D33" s="31" t="n">
         <v>6000</v>
       </c>
-      <c r="E33" s="32"/>
+      <c r="E33" s="77" t="n">
+        <v>6000</v>
+      </c>
       <c r="F33" s="20"/>
     </row>
     <row r="34" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7976,7 +8054,9 @@
       <c r="D34" s="12" t="n">
         <v>6000</v>
       </c>
-      <c r="E34" s="14"/>
+      <c r="E34" s="72" t="n">
+        <v>6000</v>
+      </c>
       <c r="F34" s="14"/>
     </row>
     <row r="35" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7989,14 +8069,14 @@
         <f aca="false">SUM(D3:D34)</f>
         <v>173500</v>
       </c>
-      <c r="E35" s="34"/>
+      <c r="E35" s="78"/>
       <c r="F35" s="1"/>
     </row>
     <row r="36" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
-      <c r="E36" s="1"/>
+      <c r="E36" s="79"/>
       <c r="F36" s="1"/>
     </row>
     <row r="37" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8005,7 +8085,7 @@
         <v>64</v>
       </c>
       <c r="C37" s="36"/>
-      <c r="E37" s="13"/>
+      <c r="E37" s="71"/>
       <c r="F37" s="1"/>
     </row>
     <row r="38" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8021,7 +8101,7 @@
       <c r="D38" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E38" s="71"/>
+      <c r="E38" s="74"/>
       <c r="F38" s="1"/>
     </row>
     <row r="39" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8037,7 +8117,7 @@
       <c r="D39" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E39" s="71"/>
+      <c r="E39" s="74"/>
       <c r="F39" s="1"/>
     </row>
     <row r="40" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8053,7 +8133,7 @@
       <c r="D40" s="26" t="n">
         <v>5000</v>
       </c>
-      <c r="E40" s="38"/>
+      <c r="E40" s="80"/>
       <c r="F40" s="1"/>
     </row>
     <row r="41" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8069,7 +8149,7 @@
       <c r="D41" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E41" s="14"/>
+      <c r="E41" s="72"/>
       <c r="F41" s="1"/>
     </row>
     <row r="42" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8085,7 +8165,7 @@
       <c r="D42" s="18" t="n">
         <v>5000</v>
       </c>
-      <c r="E42" s="71"/>
+      <c r="E42" s="74"/>
       <c r="F42" s="1"/>
     </row>
     <row r="43" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8101,7 +8181,7 @@
       <c r="D43" s="40" t="n">
         <v>8500</v>
       </c>
-      <c r="E43" s="41"/>
+      <c r="E43" s="81"/>
       <c r="F43" s="1"/>
     </row>
     <row r="44" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8115,7 +8195,7 @@
       <c r="D44" s="45" t="n">
         <v>5000</v>
       </c>
-      <c r="E44" s="72"/>
+      <c r="E44" s="82"/>
       <c r="F44" s="1"/>
     </row>
     <row r="45" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8131,7 +8211,7 @@
       <c r="D45" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E45" s="14"/>
+      <c r="E45" s="72"/>
       <c r="F45" s="1"/>
     </row>
     <row r="46" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8147,7 +8227,7 @@
       <c r="D46" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E46" s="14"/>
+      <c r="E46" s="72"/>
       <c r="F46" s="1"/>
     </row>
     <row r="47" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8160,35 +8240,35 @@
         <f aca="false">SUM(D38:D46)</f>
         <v>48500</v>
       </c>
-      <c r="E47" s="49"/>
+      <c r="E47" s="83"/>
       <c r="F47" s="1"/>
     </row>
     <row r="48" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="9"/>
       <c r="B48" s="10"/>
       <c r="C48" s="11"/>
-      <c r="E48" s="20"/>
+      <c r="E48" s="74"/>
       <c r="F48" s="1"/>
     </row>
     <row r="49" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="23"/>
       <c r="B49" s="10"/>
       <c r="C49" s="11"/>
-      <c r="E49" s="20"/>
+      <c r="E49" s="74"/>
       <c r="F49" s="1"/>
     </row>
     <row r="50" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
-      <c r="E50" s="1"/>
+      <c r="E50" s="79"/>
       <c r="F50" s="1"/>
     </row>
     <row r="51" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
-      <c r="E51" s="1"/>
+      <c r="E51" s="79"/>
       <c r="F51" s="1"/>
     </row>
     <row r="52" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8197,7 +8277,7 @@
         <v>81</v>
       </c>
       <c r="C52" s="36"/>
-      <c r="E52" s="13"/>
+      <c r="E52" s="71"/>
       <c r="F52" s="1"/>
     </row>
     <row r="53" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8213,7 +8293,7 @@
       <c r="D53" s="12" t="n">
         <v>8500</v>
       </c>
-      <c r="E53" s="20"/>
+      <c r="E53" s="74"/>
       <c r="F53" s="1"/>
     </row>
     <row r="54" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8229,7 +8309,7 @@
       <c r="D54" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E54" s="14"/>
+      <c r="E54" s="72"/>
       <c r="F54" s="1"/>
     </row>
     <row r="55" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8245,7 +8325,7 @@
       <c r="D55" s="18" t="n">
         <v>5000</v>
       </c>
-      <c r="E55" s="21"/>
+      <c r="E55" s="75"/>
       <c r="F55" s="1"/>
     </row>
     <row r="56" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8261,7 +8341,7 @@
       <c r="D56" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E56" s="71"/>
+      <c r="E56" s="74"/>
       <c r="F56" s="1"/>
     </row>
     <row r="57" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8277,7 +8357,7 @@
       <c r="D57" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E57" s="71"/>
+      <c r="E57" s="74"/>
       <c r="F57" s="1"/>
     </row>
     <row r="58" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8293,7 +8373,7 @@
       <c r="D58" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E58" s="14"/>
+      <c r="E58" s="72"/>
       <c r="F58" s="1"/>
     </row>
     <row r="59" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8309,7 +8389,7 @@
       <c r="D59" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E59" s="71"/>
+      <c r="E59" s="74"/>
       <c r="F59" s="1"/>
     </row>
     <row r="60" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8325,7 +8405,7 @@
       <c r="D60" s="18" t="n">
         <v>8500</v>
       </c>
-      <c r="E60" s="19"/>
+      <c r="E60" s="73"/>
       <c r="F60" s="1"/>
     </row>
     <row r="61" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8338,21 +8418,21 @@
         <f aca="false">SUM(D53:D60)</f>
         <v>47000</v>
       </c>
-      <c r="E61" s="50"/>
+      <c r="E61" s="84"/>
       <c r="F61" s="1"/>
     </row>
     <row r="62" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
-      <c r="E62" s="1"/>
+      <c r="E62" s="79"/>
       <c r="F62" s="1"/>
     </row>
     <row r="63" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
-      <c r="E63" s="1"/>
+      <c r="E63" s="79"/>
       <c r="F63" s="1"/>
     </row>
     <row r="64" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8361,7 +8441,7 @@
         <v>98</v>
       </c>
       <c r="C64" s="36"/>
-      <c r="E64" s="13"/>
+      <c r="E64" s="71"/>
       <c r="F64" s="1"/>
     </row>
     <row r="65" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8377,7 +8457,7 @@
       <c r="D65" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E65" s="71"/>
+      <c r="E65" s="74"/>
       <c r="F65" s="1"/>
     </row>
     <row r="66" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8393,7 +8473,7 @@
       <c r="D66" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E66" s="71"/>
+      <c r="E66" s="74"/>
       <c r="F66" s="1"/>
     </row>
     <row r="67" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8409,7 +8489,7 @@
       <c r="D67" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E67" s="73"/>
+      <c r="E67" s="72"/>
       <c r="F67" s="1"/>
     </row>
     <row r="68" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8425,7 +8505,7 @@
       <c r="D68" s="12" t="n">
         <v>8500</v>
       </c>
-      <c r="E68" s="20"/>
+      <c r="E68" s="74"/>
       <c r="F68" s="1"/>
     </row>
     <row r="69" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8441,7 +8521,7 @@
       <c r="D69" s="12" t="n">
         <v>8500</v>
       </c>
-      <c r="E69" s="20"/>
+      <c r="E69" s="74"/>
       <c r="F69" s="1"/>
     </row>
     <row r="70" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8457,7 +8537,7 @@
       <c r="D70" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E70" s="14"/>
+      <c r="E70" s="72"/>
       <c r="F70" s="1"/>
     </row>
     <row r="71" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8473,7 +8553,7 @@
       <c r="D71" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E71" s="14"/>
+      <c r="E71" s="72"/>
       <c r="F71" s="1"/>
     </row>
     <row r="72" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8489,7 +8569,7 @@
       <c r="D72" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E72" s="71"/>
+      <c r="E72" s="74"/>
       <c r="F72" s="1"/>
     </row>
     <row r="73" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8505,7 +8585,7 @@
       <c r="D73" s="18" t="n">
         <v>5000</v>
       </c>
-      <c r="E73" s="74" t="n">
+      <c r="E73" s="73" t="n">
         <v>5000</v>
       </c>
       <c r="F73" s="1"/>
@@ -8523,7 +8603,7 @@
       <c r="D74" s="18" t="n">
         <v>5000</v>
       </c>
-      <c r="E74" s="21"/>
+      <c r="E74" s="75"/>
       <c r="F74" s="1"/>
     </row>
     <row r="75" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8539,7 +8619,7 @@
       <c r="D75" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E75" s="20"/>
+      <c r="E75" s="74"/>
       <c r="F75" s="1"/>
     </row>
     <row r="76" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8555,7 +8635,7 @@
       <c r="D76" s="26" t="n">
         <v>5000</v>
       </c>
-      <c r="E76" s="75"/>
+      <c r="E76" s="76"/>
       <c r="F76" s="1"/>
     </row>
     <row r="77" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8571,7 +8651,7 @@
       <c r="D77" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E77" s="71"/>
+      <c r="E77" s="74"/>
       <c r="F77" s="1"/>
     </row>
     <row r="78" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8587,7 +8667,7 @@
       <c r="D78" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E78" s="71"/>
+      <c r="E78" s="74"/>
       <c r="F78" s="1"/>
     </row>
     <row r="79" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8595,11 +8675,11 @@
         <v>15</v>
       </c>
       <c r="B79" s="24" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C79" s="25"/>
       <c r="D79" s="26"/>
-      <c r="E79" s="75" t="n">
+      <c r="E79" s="76" t="n">
         <v>5000</v>
       </c>
       <c r="F79" s="1"/>
@@ -8613,7 +8693,7 @@
       <c r="D80" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="E80" s="13"/>
+      <c r="E80" s="71"/>
       <c r="F80" s="1"/>
     </row>
     <row r="81" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8629,7 +8709,7 @@
       <c r="D81" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E81" s="71"/>
+      <c r="E81" s="74"/>
       <c r="F81" s="1"/>
     </row>
     <row r="82" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8645,7 +8725,7 @@
       <c r="D82" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E82" s="14"/>
+      <c r="E82" s="72"/>
       <c r="F82" s="1"/>
     </row>
     <row r="83" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8661,7 +8741,7 @@
       <c r="D83" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E83" s="71"/>
+      <c r="E83" s="74"/>
       <c r="F83" s="1"/>
     </row>
     <row r="84" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8677,7 +8757,7 @@
       <c r="D84" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E84" s="20"/>
+      <c r="E84" s="74"/>
       <c r="F84" s="1"/>
     </row>
     <row r="85" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8693,7 +8773,7 @@
       <c r="D85" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E85" s="14"/>
+      <c r="E85" s="72"/>
       <c r="F85" s="1"/>
     </row>
     <row r="86" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8709,7 +8789,7 @@
       <c r="D86" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E86" s="71"/>
+      <c r="E86" s="74"/>
       <c r="F86" s="1"/>
     </row>
     <row r="87" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8722,21 +8802,21 @@
         <f aca="false">SUM(D65:D86)</f>
         <v>107000</v>
       </c>
-      <c r="E87" s="51"/>
+      <c r="E87" s="78"/>
       <c r="F87" s="1"/>
     </row>
     <row r="88" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
-      <c r="E88" s="1"/>
+      <c r="E88" s="79"/>
       <c r="F88" s="1"/>
     </row>
     <row r="89" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
-      <c r="E89" s="1"/>
+      <c r="E89" s="79"/>
       <c r="F89" s="1"/>
     </row>
     <row r="90" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8745,7 +8825,7 @@
         <v>142</v>
       </c>
       <c r="C90" s="36"/>
-      <c r="E90" s="13"/>
+      <c r="E90" s="71"/>
       <c r="F90" s="1"/>
     </row>
     <row r="91" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8761,7 +8841,7 @@
       <c r="D91" s="12" t="n">
         <v>10000</v>
       </c>
-      <c r="E91" s="20" t="n">
+      <c r="E91" s="74" t="n">
         <v>10000</v>
       </c>
       <c r="F91" s="1"/>
@@ -8779,7 +8859,7 @@
       <c r="D92" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E92" s="20" t="n">
+      <c r="E92" s="74" t="n">
         <v>11000</v>
       </c>
       <c r="F92" s="1"/>
@@ -8797,7 +8877,7 @@
       <c r="D93" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E93" s="20"/>
+      <c r="E93" s="74"/>
       <c r="F93" s="1"/>
     </row>
     <row r="94" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8813,7 +8893,7 @@
       <c r="D94" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E94" s="14"/>
+      <c r="E94" s="72"/>
       <c r="F94" s="1"/>
     </row>
     <row r="95" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8829,7 +8909,7 @@
       <c r="D95" s="26" t="n">
         <v>11000</v>
       </c>
-      <c r="E95" s="38"/>
+      <c r="E95" s="80"/>
       <c r="F95" s="1"/>
     </row>
     <row r="96" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8843,7 +8923,7 @@
       <c r="D96" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E96" s="20"/>
+      <c r="E96" s="74"/>
       <c r="F96" s="1"/>
     </row>
     <row r="97" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8859,7 +8939,7 @@
       <c r="D97" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E97" s="14"/>
+      <c r="E97" s="72"/>
       <c r="F97" s="1"/>
     </row>
     <row r="98" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8875,7 +8955,7 @@
       <c r="D98" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E98" s="20"/>
+      <c r="E98" s="74"/>
       <c r="F98" s="1"/>
     </row>
     <row r="99" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8891,7 +8971,7 @@
       <c r="D99" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E99" s="14"/>
+      <c r="E99" s="72"/>
       <c r="F99" s="1"/>
     </row>
     <row r="100" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8907,7 +8987,7 @@
       <c r="D100" s="12" t="n">
         <v>13000</v>
       </c>
-      <c r="E100" s="20"/>
+      <c r="E100" s="74"/>
       <c r="F100" s="1"/>
     </row>
     <row r="101" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8923,7 +9003,7 @@
       <c r="D101" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E101" s="14"/>
+      <c r="E101" s="72"/>
       <c r="F101" s="1"/>
     </row>
     <row r="102" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8939,7 +9019,7 @@
       <c r="D102" s="53" t="n">
         <v>10000</v>
       </c>
-      <c r="E102" s="14"/>
+      <c r="E102" s="72"/>
       <c r="F102" s="1"/>
     </row>
     <row r="103" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8955,7 +9035,7 @@
       <c r="D103" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E103" s="20"/>
+      <c r="E103" s="74"/>
       <c r="F103" s="1"/>
     </row>
     <row r="104" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8971,7 +9051,7 @@
       <c r="D104" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E104" s="14"/>
+      <c r="E104" s="72"/>
       <c r="F104" s="1"/>
     </row>
     <row r="105" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8984,28 +9064,28 @@
         <f aca="false">SUM(D91:D104)</f>
         <v>154000</v>
       </c>
-      <c r="E105" s="51"/>
+      <c r="E105" s="78"/>
       <c r="F105" s="1"/>
     </row>
     <row r="106" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
-      <c r="E106" s="1"/>
+      <c r="E106" s="79"/>
       <c r="F106" s="1"/>
     </row>
     <row r="107" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
-      <c r="E107" s="1"/>
+      <c r="E107" s="79"/>
       <c r="F107" s="1"/>
     </row>
     <row r="108" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
-      <c r="E108" s="1"/>
+      <c r="E108" s="79"/>
       <c r="F108" s="1"/>
     </row>
     <row r="109" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9014,7 +9094,7 @@
         <v>168</v>
       </c>
       <c r="C109" s="36"/>
-      <c r="E109" s="13"/>
+      <c r="E109" s="71"/>
       <c r="F109" s="1"/>
     </row>
     <row r="110" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9030,7 +9110,7 @@
       <c r="D110" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E110" s="14"/>
+      <c r="E110" s="72"/>
       <c r="F110" s="1"/>
     </row>
     <row r="111" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9046,7 +9126,7 @@
       <c r="D111" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E111" s="14"/>
+      <c r="E111" s="72"/>
       <c r="F111" s="1"/>
     </row>
     <row r="112" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9062,7 +9142,7 @@
       <c r="D112" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E112" s="20"/>
+      <c r="E112" s="74"/>
       <c r="F112" s="1"/>
     </row>
     <row r="113" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9078,7 +9158,7 @@
       <c r="D113" s="12" t="n">
         <v>14000</v>
       </c>
-      <c r="E113" s="20"/>
+      <c r="E113" s="74"/>
       <c r="F113" s="1"/>
     </row>
     <row r="114" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9094,7 +9174,7 @@
       <c r="D114" s="26" t="n">
         <v>11000</v>
       </c>
-      <c r="E114" s="27"/>
+      <c r="E114" s="76"/>
       <c r="F114" s="1"/>
     </row>
     <row r="115" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9110,7 +9190,7 @@
       <c r="D115" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E115" s="14"/>
+      <c r="E115" s="72"/>
       <c r="F115" s="1"/>
     </row>
     <row r="116" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9126,7 +9206,7 @@
       <c r="D116" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E116" s="20"/>
+      <c r="E116" s="74"/>
       <c r="F116" s="1"/>
     </row>
     <row r="117" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9142,7 +9222,7 @@
       <c r="D117" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E117" s="14"/>
+      <c r="E117" s="72"/>
       <c r="F117" s="1"/>
     </row>
     <row r="118" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9158,7 +9238,7 @@
       <c r="D118" s="18" t="n">
         <v>14000</v>
       </c>
-      <c r="E118" s="21"/>
+      <c r="E118" s="75"/>
       <c r="F118" s="1"/>
     </row>
     <row r="119" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9174,7 +9254,7 @@
       <c r="D119" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E119" s="20"/>
+      <c r="E119" s="74"/>
       <c r="F119" s="1"/>
     </row>
     <row r="120" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9190,7 +9270,7 @@
       <c r="D120" s="18" t="n">
         <v>11000</v>
       </c>
-      <c r="E120" s="19"/>
+      <c r="E120" s="73"/>
       <c r="F120" s="1"/>
     </row>
     <row r="121" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9206,7 +9286,7 @@
       <c r="D121" s="18" t="n">
         <v>11000</v>
       </c>
-      <c r="E121" s="19" t="n">
+      <c r="E121" s="73" t="n">
         <v>11000</v>
       </c>
       <c r="F121" s="1"/>
@@ -9224,7 +9304,7 @@
       <c r="D122" s="18" t="n">
         <v>11000</v>
       </c>
-      <c r="E122" s="19"/>
+      <c r="E122" s="73"/>
       <c r="F122" s="1"/>
     </row>
     <row r="123" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9240,7 +9320,7 @@
       <c r="D123" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E123" s="14"/>
+      <c r="E123" s="72"/>
       <c r="F123" s="55"/>
     </row>
     <row r="124" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9248,7 +9328,7 @@
         <v>15</v>
       </c>
       <c r="B124" s="10" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C124" s="11" t="n">
         <v>740808927</v>
@@ -9256,7 +9336,7 @@
       <c r="D124" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E124" s="20"/>
+      <c r="E124" s="74"/>
       <c r="F124" s="1"/>
     </row>
     <row r="125" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9272,7 +9352,7 @@
       <c r="D125" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E125" s="20"/>
+      <c r="E125" s="74"/>
       <c r="F125" s="1"/>
     </row>
     <row r="126" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9288,7 +9368,7 @@
       <c r="D126" s="12" t="n">
         <v>14000</v>
       </c>
-      <c r="E126" s="20"/>
+      <c r="E126" s="74"/>
       <c r="F126" s="1"/>
     </row>
     <row r="127" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9304,7 +9384,7 @@
       <c r="D127" s="18" t="n">
         <v>11000</v>
       </c>
-      <c r="E127" s="21"/>
+      <c r="E127" s="75"/>
       <c r="F127" s="1"/>
     </row>
     <row r="128" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9320,7 +9400,7 @@
       <c r="D128" s="18" t="n">
         <v>11000</v>
       </c>
-      <c r="E128" s="21"/>
+      <c r="E128" s="75"/>
       <c r="F128" s="1"/>
     </row>
     <row r="129" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9336,7 +9416,7 @@
       <c r="D129" s="18" t="n">
         <v>11000</v>
       </c>
-      <c r="E129" s="19"/>
+      <c r="E129" s="73"/>
       <c r="F129" s="1"/>
     </row>
     <row r="130" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9352,7 +9432,7 @@
       <c r="D130" s="12" t="n">
         <v>16000</v>
       </c>
-      <c r="E130" s="14"/>
+      <c r="E130" s="72"/>
       <c r="F130" s="1"/>
     </row>
     <row r="131" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9365,9 +9445,9 @@
         <f aca="false">SUM(D110:D130)</f>
         <v>245000</v>
       </c>
-      <c r="E131" s="76" t="n">
+      <c r="E131" s="85" t="n">
         <f aca="false">SUM(E3:E129)</f>
-        <v>42000</v>
+        <v>122000</v>
       </c>
       <c r="F131" s="1"/>
     </row>
@@ -9394,7 +9474,7 @@
       <c r="D134" s="69" t="n">
         <v>775000</v>
       </c>
-      <c r="E134" s="77" t="n">
+      <c r="E134" s="86" t="n">
         <v>775000</v>
       </c>
       <c r="F134" s="61"/>

--- a/PROPERTIES/MONICA/MONICA2025.xlsx
+++ b/PROPERTIES/MONICA/MONICA2025.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="226">
   <si>
     <t xml:space="preserve">HOUSE NO</t>
   </si>
@@ -694,6 +694,9 @@
   </si>
   <si>
     <t xml:space="preserve">get name???</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DORINE</t>
   </si>
   <si>
     <t xml:space="preserve">PHOEBE</t>
@@ -709,7 +712,7 @@
     <numFmt numFmtId="166" formatCode="#,##0.00"/>
     <numFmt numFmtId="167" formatCode="#,##0"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -862,6 +865,13 @@
     </font>
     <font>
       <b val="true"/>
+      <sz val="10.5"/>
+      <color rgb="FF008000"/>
+      <name val="Georgia"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
       <u val="single"/>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -999,7 +1009,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="92">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1340,11 +1350,31 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="166" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="21" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="21" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="21" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="167" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="22" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -7590,7 +7620,9 @@
       <c r="D6" s="12" t="n">
         <v>8500</v>
       </c>
-      <c r="E6" s="72"/>
+      <c r="E6" s="72" t="n">
+        <v>8500</v>
+      </c>
       <c r="F6" s="14"/>
     </row>
     <row r="7" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7606,7 +7638,9 @@
       <c r="D7" s="18" t="n">
         <v>5000</v>
       </c>
-      <c r="E7" s="73"/>
+      <c r="E7" s="73" t="n">
+        <v>5000</v>
+      </c>
       <c r="F7" s="19"/>
     </row>
     <row r="8" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7656,7 +7690,9 @@
       <c r="D10" s="18" t="n">
         <v>5000</v>
       </c>
-      <c r="E10" s="75"/>
+      <c r="E10" s="75" t="n">
+        <v>5000</v>
+      </c>
       <c r="F10" s="21"/>
     </row>
     <row r="11" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7754,7 +7790,9 @@
       <c r="D16" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E16" s="74"/>
+      <c r="E16" s="74" t="n">
+        <v>5000</v>
+      </c>
       <c r="F16" s="20"/>
     </row>
     <row r="17" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7852,7 +7890,9 @@
       <c r="D22" s="18" t="n">
         <v>5000</v>
       </c>
-      <c r="E22" s="73"/>
+      <c r="E22" s="73" t="n">
+        <v>5000</v>
+      </c>
       <c r="F22" s="19"/>
     </row>
     <row r="23" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7886,7 +7926,9 @@
       <c r="D24" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E24" s="74"/>
+      <c r="E24" s="74" t="n">
+        <v>5000</v>
+      </c>
       <c r="F24" s="20"/>
     </row>
     <row r="25" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7954,7 +7996,9 @@
       <c r="D28" s="18" t="n">
         <v>6000</v>
       </c>
-      <c r="E28" s="73"/>
+      <c r="E28" s="73" t="n">
+        <v>6000</v>
+      </c>
       <c r="F28" s="19"/>
     </row>
     <row r="29" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8020,7 +8064,9 @@
       <c r="D32" s="26" t="n">
         <v>6000</v>
       </c>
-      <c r="E32" s="76"/>
+      <c r="E32" s="76" t="n">
+        <v>6000</v>
+      </c>
       <c r="F32" s="27"/>
     </row>
     <row r="33" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8101,7 +8147,9 @@
       <c r="D38" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E38" s="74"/>
+      <c r="E38" s="74" t="n">
+        <v>5000</v>
+      </c>
       <c r="F38" s="1"/>
     </row>
     <row r="39" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8117,7 +8165,9 @@
       <c r="D39" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E39" s="74"/>
+      <c r="E39" s="74" t="n">
+        <v>5000</v>
+      </c>
       <c r="F39" s="1"/>
     </row>
     <row r="40" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8133,7 +8183,9 @@
       <c r="D40" s="26" t="n">
         <v>5000</v>
       </c>
-      <c r="E40" s="80"/>
+      <c r="E40" s="80" t="n">
+        <v>5000</v>
+      </c>
       <c r="F40" s="1"/>
     </row>
     <row r="41" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8149,7 +8201,9 @@
       <c r="D41" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E41" s="72"/>
+      <c r="E41" s="72" t="n">
+        <v>5000</v>
+      </c>
       <c r="F41" s="1"/>
     </row>
     <row r="42" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8165,7 +8219,9 @@
       <c r="D42" s="18" t="n">
         <v>5000</v>
       </c>
-      <c r="E42" s="74"/>
+      <c r="E42" s="74" t="n">
+        <v>5000</v>
+      </c>
       <c r="F42" s="1"/>
     </row>
     <row r="43" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8181,7 +8237,9 @@
       <c r="D43" s="40" t="n">
         <v>8500</v>
       </c>
-      <c r="E43" s="81"/>
+      <c r="E43" s="81" t="n">
+        <v>8500</v>
+      </c>
       <c r="F43" s="1"/>
     </row>
     <row r="44" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8195,7 +8253,9 @@
       <c r="D44" s="45" t="n">
         <v>5000</v>
       </c>
-      <c r="E44" s="82"/>
+      <c r="E44" s="82" t="n">
+        <v>5000</v>
+      </c>
       <c r="F44" s="1"/>
     </row>
     <row r="45" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8211,7 +8271,9 @@
       <c r="D45" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E45" s="72"/>
+      <c r="E45" s="72" t="n">
+        <v>5000</v>
+      </c>
       <c r="F45" s="1"/>
     </row>
     <row r="46" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8227,7 +8289,9 @@
       <c r="D46" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E46" s="72"/>
+      <c r="E46" s="72" t="n">
+        <v>5000</v>
+      </c>
       <c r="F46" s="1"/>
     </row>
     <row r="47" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8309,7 +8373,9 @@
       <c r="D54" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E54" s="72"/>
+      <c r="E54" s="72" t="n">
+        <v>5000</v>
+      </c>
       <c r="F54" s="1"/>
     </row>
     <row r="55" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8325,7 +8391,9 @@
       <c r="D55" s="18" t="n">
         <v>5000</v>
       </c>
-      <c r="E55" s="75"/>
+      <c r="E55" s="75" t="n">
+        <v>5000</v>
+      </c>
       <c r="F55" s="1"/>
     </row>
     <row r="56" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8341,7 +8409,9 @@
       <c r="D56" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E56" s="74"/>
+      <c r="E56" s="74" t="n">
+        <v>5000</v>
+      </c>
       <c r="F56" s="1"/>
     </row>
     <row r="57" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8357,7 +8427,9 @@
       <c r="D57" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E57" s="74"/>
+      <c r="E57" s="74" t="n">
+        <v>5000</v>
+      </c>
       <c r="F57" s="1"/>
     </row>
     <row r="58" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8373,7 +8445,9 @@
       <c r="D58" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E58" s="72"/>
+      <c r="E58" s="72" t="n">
+        <v>5000</v>
+      </c>
       <c r="F58" s="1"/>
     </row>
     <row r="59" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8405,7 +8479,9 @@
       <c r="D60" s="18" t="n">
         <v>8500</v>
       </c>
-      <c r="E60" s="73"/>
+      <c r="E60" s="73" t="n">
+        <v>8500</v>
+      </c>
       <c r="F60" s="1"/>
     </row>
     <row r="61" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8457,7 +8533,9 @@
       <c r="D65" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E65" s="74"/>
+      <c r="E65" s="74" t="n">
+        <v>5000</v>
+      </c>
       <c r="F65" s="1"/>
     </row>
     <row r="66" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8473,7 +8551,9 @@
       <c r="D66" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E66" s="74"/>
+      <c r="E66" s="74" t="n">
+        <v>5000</v>
+      </c>
       <c r="F66" s="1"/>
     </row>
     <row r="67" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8489,7 +8569,9 @@
       <c r="D67" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E67" s="72"/>
+      <c r="E67" s="72" t="n">
+        <v>5000</v>
+      </c>
       <c r="F67" s="1"/>
     </row>
     <row r="68" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8521,7 +8603,9 @@
       <c r="D69" s="12" t="n">
         <v>8500</v>
       </c>
-      <c r="E69" s="74"/>
+      <c r="E69" s="74" t="n">
+        <v>8500</v>
+      </c>
       <c r="F69" s="1"/>
     </row>
     <row r="70" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8537,7 +8621,9 @@
       <c r="D70" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E70" s="72"/>
+      <c r="E70" s="72" t="n">
+        <v>5000</v>
+      </c>
       <c r="F70" s="1"/>
     </row>
     <row r="71" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8603,7 +8689,9 @@
       <c r="D74" s="18" t="n">
         <v>5000</v>
       </c>
-      <c r="E74" s="75"/>
+      <c r="E74" s="75" t="n">
+        <v>5000</v>
+      </c>
       <c r="F74" s="1"/>
     </row>
     <row r="75" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8619,7 +8707,9 @@
       <c r="D75" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E75" s="74"/>
+      <c r="E75" s="74" t="n">
+        <v>5000</v>
+      </c>
       <c r="F75" s="1"/>
     </row>
     <row r="76" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8651,7 +8741,9 @@
       <c r="D77" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E77" s="74"/>
+      <c r="E77" s="74" t="n">
+        <v>5000</v>
+      </c>
       <c r="F77" s="1"/>
     </row>
     <row r="78" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8667,7 +8759,9 @@
       <c r="D78" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E78" s="74"/>
+      <c r="E78" s="74" t="n">
+        <v>5000</v>
+      </c>
       <c r="F78" s="1"/>
     </row>
     <row r="79" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8709,7 +8803,9 @@
       <c r="D81" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E81" s="74"/>
+      <c r="E81" s="74" t="n">
+        <v>5000</v>
+      </c>
       <c r="F81" s="1"/>
     </row>
     <row r="82" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8725,7 +8821,9 @@
       <c r="D82" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E82" s="72"/>
+      <c r="E82" s="72" t="n">
+        <v>5000</v>
+      </c>
       <c r="F82" s="1"/>
     </row>
     <row r="83" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8757,7 +8855,9 @@
       <c r="D84" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E84" s="74"/>
+      <c r="E84" s="74" t="n">
+        <v>5000</v>
+      </c>
       <c r="F84" s="1"/>
     </row>
     <row r="85" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8773,7 +8873,9 @@
       <c r="D85" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E85" s="72"/>
+      <c r="E85" s="72" t="n">
+        <v>5000</v>
+      </c>
       <c r="F85" s="1"/>
     </row>
     <row r="86" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8789,7 +8891,9 @@
       <c r="D86" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E86" s="74"/>
+      <c r="E86" s="74" t="n">
+        <v>5000</v>
+      </c>
       <c r="F86" s="1"/>
     </row>
     <row r="87" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8877,7 +8981,9 @@
       <c r="D93" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E93" s="74"/>
+      <c r="E93" s="74" t="n">
+        <v>11000</v>
+      </c>
       <c r="F93" s="1"/>
     </row>
     <row r="94" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8893,7 +8999,9 @@
       <c r="D94" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E94" s="72"/>
+      <c r="E94" s="72" t="n">
+        <v>11000</v>
+      </c>
       <c r="F94" s="1"/>
     </row>
     <row r="95" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8909,7 +9017,9 @@
       <c r="D95" s="26" t="n">
         <v>11000</v>
       </c>
-      <c r="E95" s="80"/>
+      <c r="E95" s="80" t="n">
+        <v>11000</v>
+      </c>
       <c r="F95" s="1"/>
     </row>
     <row r="96" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8917,13 +9027,17 @@
         <v>6</v>
       </c>
       <c r="B96" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="C96" s="11"/>
+        <v>224</v>
+      </c>
+      <c r="C96" s="11" t="n">
+        <v>796923935</v>
+      </c>
       <c r="D96" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E96" s="74"/>
+      <c r="E96" s="74" t="n">
+        <v>11000</v>
+      </c>
       <c r="F96" s="1"/>
     </row>
     <row r="97" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8939,7 +9053,9 @@
       <c r="D97" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E97" s="72"/>
+      <c r="E97" s="72" t="n">
+        <v>11000</v>
+      </c>
       <c r="F97" s="1"/>
     </row>
     <row r="98" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8955,7 +9071,9 @@
       <c r="D98" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E98" s="74"/>
+      <c r="E98" s="74" t="n">
+        <v>11000</v>
+      </c>
       <c r="F98" s="1"/>
     </row>
     <row r="99" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8971,7 +9089,9 @@
       <c r="D99" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E99" s="72"/>
+      <c r="E99" s="72" t="n">
+        <v>11000</v>
+      </c>
       <c r="F99" s="1"/>
     </row>
     <row r="100" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8987,7 +9107,9 @@
       <c r="D100" s="12" t="n">
         <v>13000</v>
       </c>
-      <c r="E100" s="74"/>
+      <c r="E100" s="74" t="n">
+        <v>13000</v>
+      </c>
       <c r="F100" s="1"/>
     </row>
     <row r="101" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9003,7 +9125,9 @@
       <c r="D101" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E101" s="72"/>
+      <c r="E101" s="72" t="n">
+        <v>11000</v>
+      </c>
       <c r="F101" s="1"/>
     </row>
     <row r="102" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9019,7 +9143,9 @@
       <c r="D102" s="53" t="n">
         <v>10000</v>
       </c>
-      <c r="E102" s="72"/>
+      <c r="E102" s="72" t="n">
+        <v>10000</v>
+      </c>
       <c r="F102" s="1"/>
     </row>
     <row r="103" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9035,7 +9161,9 @@
       <c r="D103" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E103" s="74"/>
+      <c r="E103" s="74" t="n">
+        <v>11000</v>
+      </c>
       <c r="F103" s="1"/>
     </row>
     <row r="104" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9051,7 +9179,9 @@
       <c r="D104" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E104" s="72"/>
+      <c r="E104" s="72" t="n">
+        <v>11000</v>
+      </c>
       <c r="F104" s="1"/>
     </row>
     <row r="105" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9110,7 +9240,9 @@
       <c r="D110" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E110" s="72"/>
+      <c r="E110" s="72" t="n">
+        <v>11000</v>
+      </c>
       <c r="F110" s="1"/>
     </row>
     <row r="111" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9126,7 +9258,9 @@
       <c r="D111" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E111" s="72"/>
+      <c r="E111" s="85" t="n">
+        <v>11000</v>
+      </c>
       <c r="F111" s="1"/>
     </row>
     <row r="112" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9142,7 +9276,9 @@
       <c r="D112" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E112" s="74"/>
+      <c r="E112" s="86" t="n">
+        <v>11000</v>
+      </c>
       <c r="F112" s="1"/>
     </row>
     <row r="113" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9158,7 +9294,9 @@
       <c r="D113" s="12" t="n">
         <v>14000</v>
       </c>
-      <c r="E113" s="74"/>
+      <c r="E113" s="86" t="n">
+        <v>11000</v>
+      </c>
       <c r="F113" s="1"/>
     </row>
     <row r="114" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9174,7 +9312,9 @@
       <c r="D114" s="26" t="n">
         <v>11000</v>
       </c>
-      <c r="E114" s="76"/>
+      <c r="E114" s="87" t="n">
+        <v>11000</v>
+      </c>
       <c r="F114" s="1"/>
     </row>
     <row r="115" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9190,7 +9330,9 @@
       <c r="D115" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E115" s="72"/>
+      <c r="E115" s="85" t="n">
+        <v>11000</v>
+      </c>
       <c r="F115" s="1"/>
     </row>
     <row r="116" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9206,7 +9348,9 @@
       <c r="D116" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E116" s="74"/>
+      <c r="E116" s="86" t="n">
+        <v>11000</v>
+      </c>
       <c r="F116" s="1"/>
     </row>
     <row r="117" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9222,7 +9366,9 @@
       <c r="D117" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E117" s="72"/>
+      <c r="E117" s="85" t="n">
+        <v>11000</v>
+      </c>
       <c r="F117" s="1"/>
     </row>
     <row r="118" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9238,7 +9384,9 @@
       <c r="D118" s="18" t="n">
         <v>14000</v>
       </c>
-      <c r="E118" s="75"/>
+      <c r="E118" s="88" t="n">
+        <v>11000</v>
+      </c>
       <c r="F118" s="1"/>
     </row>
     <row r="119" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9254,7 +9402,7 @@
       <c r="D119" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E119" s="74"/>
+      <c r="E119" s="86"/>
       <c r="F119" s="1"/>
     </row>
     <row r="120" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9270,7 +9418,9 @@
       <c r="D120" s="18" t="n">
         <v>11000</v>
       </c>
-      <c r="E120" s="73"/>
+      <c r="E120" s="89" t="n">
+        <v>11000</v>
+      </c>
       <c r="F120" s="1"/>
     </row>
     <row r="121" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9304,7 +9454,7 @@
       <c r="D122" s="18" t="n">
         <v>11000</v>
       </c>
-      <c r="E122" s="73"/>
+      <c r="E122" s="89"/>
       <c r="F122" s="1"/>
     </row>
     <row r="123" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9320,7 +9470,9 @@
       <c r="D123" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E123" s="72"/>
+      <c r="E123" s="85" t="n">
+        <v>11000</v>
+      </c>
       <c r="F123" s="55"/>
     </row>
     <row r="124" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9328,7 +9480,7 @@
         <v>15</v>
       </c>
       <c r="B124" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C124" s="11" t="n">
         <v>740808927</v>
@@ -9336,7 +9488,9 @@
       <c r="D124" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E124" s="74"/>
+      <c r="E124" s="86" t="n">
+        <v>11000</v>
+      </c>
       <c r="F124" s="1"/>
     </row>
     <row r="125" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9352,7 +9506,9 @@
       <c r="D125" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E125" s="74"/>
+      <c r="E125" s="86" t="n">
+        <v>11000</v>
+      </c>
       <c r="F125" s="1"/>
     </row>
     <row r="126" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9368,7 +9524,9 @@
       <c r="D126" s="12" t="n">
         <v>14000</v>
       </c>
-      <c r="E126" s="74"/>
+      <c r="E126" s="86" t="n">
+        <v>11000</v>
+      </c>
       <c r="F126" s="1"/>
     </row>
     <row r="127" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9384,7 +9542,9 @@
       <c r="D127" s="18" t="n">
         <v>11000</v>
       </c>
-      <c r="E127" s="75"/>
+      <c r="E127" s="88" t="n">
+        <v>11000</v>
+      </c>
       <c r="F127" s="1"/>
     </row>
     <row r="128" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9400,7 +9560,9 @@
       <c r="D128" s="18" t="n">
         <v>11000</v>
       </c>
-      <c r="E128" s="75"/>
+      <c r="E128" s="88" t="n">
+        <v>11000</v>
+      </c>
       <c r="F128" s="1"/>
     </row>
     <row r="129" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9416,7 +9578,9 @@
       <c r="D129" s="18" t="n">
         <v>11000</v>
       </c>
-      <c r="E129" s="73"/>
+      <c r="E129" s="89" t="n">
+        <v>11000</v>
+      </c>
       <c r="F129" s="1"/>
     </row>
     <row r="130" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9432,7 +9596,9 @@
       <c r="D130" s="12" t="n">
         <v>16000</v>
       </c>
-      <c r="E130" s="72"/>
+      <c r="E130" s="85" t="n">
+        <v>11000</v>
+      </c>
       <c r="F130" s="1"/>
     </row>
     <row r="131" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9445,10 +9611,7 @@
         <f aca="false">SUM(D110:D130)</f>
         <v>245000</v>
       </c>
-      <c r="E131" s="85" t="n">
-        <f aca="false">SUM(E3:E129)</f>
-        <v>122000</v>
-      </c>
+      <c r="E131" s="90"/>
       <c r="F131" s="1"/>
     </row>
     <row r="132" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9474,8 +9637,9 @@
       <c r="D134" s="69" t="n">
         <v>775000</v>
       </c>
-      <c r="E134" s="86" t="n">
-        <v>775000</v>
+      <c r="E134" s="91" t="n">
+        <f aca="false">SUM(E4:E133)</f>
+        <v>654000</v>
       </c>
       <c r="F134" s="61"/>
     </row>

--- a/PROPERTIES/MONICA/MONICA2025.xlsx
+++ b/PROPERTIES/MONICA/MONICA2025.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="227">
   <si>
     <t xml:space="preserve">HOUSE NO</t>
   </si>
@@ -687,13 +687,16 @@
     <t xml:space="preserve">NO TEXT YET</t>
   </si>
   <si>
-    <t xml:space="preserve">AUG</t>
+    <t xml:space="preserve">AUGUST</t>
   </si>
   <si>
     <t xml:space="preserve">????</t>
   </si>
   <si>
-    <t xml:space="preserve">get name???</t>
+    <t xml:space="preserve">JOHN MAKABAU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VACANT</t>
   </si>
   <si>
     <t xml:space="preserve">DORINE</t>
@@ -712,7 +715,7 @@
     <numFmt numFmtId="166" formatCode="#,##0.00"/>
     <numFmt numFmtId="167" formatCode="#,##0"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="27">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -847,9 +850,23 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="10"/>
+      <name val="Georgia"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <b val="true"/>
       <sz val="10.5"/>
       <color rgb="FF008000"/>
+      <name val="Georgia"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Georgia"/>
       <family val="1"/>
       <charset val="1"/>
@@ -865,16 +882,29 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="10.5"/>
-      <color rgb="FF008000"/>
+      <sz val="11"/>
       <name val="Georgia"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
-      <u val="single"/>
-      <sz val="12"/>
+      <sz val="15"/>
       <color rgb="FF000000"/>
+      <name val="Georgia"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="14"/>
+      <name val="Georgia"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="15"/>
       <name val="Georgia"/>
       <family val="1"/>
       <charset val="1"/>
@@ -1009,7 +1039,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="93">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1294,31 +1324,67 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="19" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="19" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="20" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="19" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="19" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="20" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="20" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="20" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="20" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="20" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="20" fillId="11" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1326,55 +1392,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="19" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="19" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="11" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="21" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="21" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="21" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="167" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -7518,11 +7552,13 @@
   <dimension ref="A1:F138"/>
   <sheetFormatPr defaultColWidth="11.5625" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="62" width="41.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="62" width="29.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="62" width="24.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="62" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="62" width="32.11"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="71" width="11.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="72" width="41.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="72" width="29.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="72" width="24.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="72" width="27.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="72" width="32.11"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="7" style="71" width="11.56"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7568,7 +7604,9 @@
       <c r="D3" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E3" s="71"/>
+      <c r="E3" s="73" t="n">
+        <v>5000</v>
+      </c>
       <c r="F3" s="13"/>
     </row>
     <row r="4" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7584,7 +7622,7 @@
       <c r="D4" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E4" s="71" t="n">
+      <c r="E4" s="73" t="n">
         <v>5000</v>
       </c>
       <c r="F4" s="13"/>
@@ -7602,7 +7640,7 @@
       <c r="D5" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E5" s="72" t="n">
+      <c r="E5" s="74" t="n">
         <v>5000</v>
       </c>
       <c r="F5" s="14"/>
@@ -7620,7 +7658,7 @@
       <c r="D6" s="12" t="n">
         <v>8500</v>
       </c>
-      <c r="E6" s="72" t="n">
+      <c r="E6" s="74" t="n">
         <v>8500</v>
       </c>
       <c r="F6" s="14"/>
@@ -7638,7 +7676,7 @@
       <c r="D7" s="18" t="n">
         <v>5000</v>
       </c>
-      <c r="E7" s="73" t="n">
+      <c r="E7" s="75" t="n">
         <v>5000</v>
       </c>
       <c r="F7" s="19"/>
@@ -7656,7 +7694,7 @@
       <c r="D8" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E8" s="74" t="n">
+      <c r="E8" s="76" t="n">
         <v>5000</v>
       </c>
       <c r="F8" s="20"/>
@@ -7672,7 +7710,7 @@
       <c r="D9" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E9" s="74" t="n">
+      <c r="E9" s="76" t="n">
         <v>5000</v>
       </c>
       <c r="F9" s="20"/>
@@ -7690,7 +7728,7 @@
       <c r="D10" s="18" t="n">
         <v>5000</v>
       </c>
-      <c r="E10" s="75" t="n">
+      <c r="E10" s="77" t="n">
         <v>5000</v>
       </c>
       <c r="F10" s="21"/>
@@ -7708,7 +7746,9 @@
       <c r="D11" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E11" s="74"/>
+      <c r="E11" s="76" t="n">
+        <v>5000</v>
+      </c>
       <c r="F11" s="20"/>
     </row>
     <row r="12" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7724,7 +7764,7 @@
       <c r="D12" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E12" s="72" t="n">
+      <c r="E12" s="74" t="n">
         <v>5000</v>
       </c>
       <c r="F12" s="14"/>
@@ -7742,7 +7782,7 @@
       <c r="D13" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E13" s="72" t="n">
+      <c r="E13" s="74" t="n">
         <v>5000</v>
       </c>
       <c r="F13" s="14"/>
@@ -7752,13 +7792,17 @@
         <v>12</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" s="11"/>
+        <v>223</v>
+      </c>
+      <c r="C14" s="11" t="n">
+        <v>724027615</v>
+      </c>
       <c r="D14" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E14" s="74"/>
+      <c r="E14" s="76" t="n">
+        <v>5000</v>
+      </c>
       <c r="F14" s="20"/>
     </row>
     <row r="15" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7774,7 +7818,9 @@
       <c r="D15" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E15" s="74"/>
+      <c r="E15" s="76" t="n">
+        <v>5000</v>
+      </c>
       <c r="F15" s="20"/>
     </row>
     <row r="16" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7790,7 +7836,7 @@
       <c r="D16" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E16" s="74" t="n">
+      <c r="E16" s="76" t="n">
         <v>5000</v>
       </c>
       <c r="F16" s="20"/>
@@ -7804,7 +7850,9 @@
       <c r="D17" s="18" t="n">
         <v>5000</v>
       </c>
-      <c r="E17" s="73"/>
+      <c r="E17" s="75" t="n">
+        <v>5000</v>
+      </c>
       <c r="F17" s="19"/>
     </row>
     <row r="18" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7820,7 +7868,7 @@
       <c r="D18" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E18" s="72" t="n">
+      <c r="E18" s="74" t="n">
         <v>5000</v>
       </c>
       <c r="F18" s="14"/>
@@ -7838,7 +7886,7 @@
       <c r="D19" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E19" s="72" t="n">
+      <c r="E19" s="74" t="n">
         <v>5000</v>
       </c>
       <c r="F19" s="14"/>
@@ -7856,7 +7904,7 @@
       <c r="D20" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E20" s="72" t="n">
+      <c r="E20" s="74" t="n">
         <v>5000</v>
       </c>
       <c r="F20" s="14"/>
@@ -7874,7 +7922,9 @@
       <c r="D21" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E21" s="74"/>
+      <c r="E21" s="76" t="n">
+        <v>5000</v>
+      </c>
       <c r="F21" s="20"/>
     </row>
     <row r="22" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7890,7 +7940,7 @@
       <c r="D22" s="18" t="n">
         <v>5000</v>
       </c>
-      <c r="E22" s="73" t="n">
+      <c r="E22" s="75" t="n">
         <v>5000</v>
       </c>
       <c r="F22" s="19"/>
@@ -7908,7 +7958,7 @@
       <c r="D23" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E23" s="72" t="n">
+      <c r="E23" s="74" t="n">
         <v>5000</v>
       </c>
       <c r="F23" s="14"/>
@@ -7926,7 +7976,7 @@
       <c r="D24" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E24" s="74" t="n">
+      <c r="E24" s="76" t="n">
         <v>5000</v>
       </c>
       <c r="F24" s="20"/>
@@ -7944,7 +7994,7 @@
       <c r="D25" s="12" t="n">
         <v>6000</v>
       </c>
-      <c r="E25" s="74" t="n">
+      <c r="E25" s="76" t="n">
         <v>6000</v>
       </c>
       <c r="F25" s="20"/>
@@ -7962,7 +8012,9 @@
       <c r="D26" s="18" t="n">
         <v>6000</v>
       </c>
-      <c r="E26" s="73"/>
+      <c r="E26" s="75" t="n">
+        <v>6000</v>
+      </c>
       <c r="F26" s="19"/>
     </row>
     <row r="27" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7978,7 +8030,7 @@
       <c r="D27" s="12" t="n">
         <v>6000</v>
       </c>
-      <c r="E27" s="72" t="n">
+      <c r="E27" s="74" t="n">
         <v>6000</v>
       </c>
       <c r="F27" s="14"/>
@@ -7996,7 +8048,7 @@
       <c r="D28" s="18" t="n">
         <v>6000</v>
       </c>
-      <c r="E28" s="73" t="n">
+      <c r="E28" s="75" t="n">
         <v>6000</v>
       </c>
       <c r="F28" s="19"/>
@@ -8014,7 +8066,7 @@
       <c r="D29" s="12" t="n">
         <v>6000</v>
       </c>
-      <c r="E29" s="72" t="n">
+      <c r="E29" s="74" t="n">
         <v>6000</v>
       </c>
       <c r="F29" s="14"/>
@@ -8032,7 +8084,9 @@
       <c r="D30" s="12" t="n">
         <v>6000</v>
       </c>
-      <c r="E30" s="72"/>
+      <c r="E30" s="74" t="n">
+        <v>6000</v>
+      </c>
       <c r="F30" s="14"/>
     </row>
     <row r="31" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8048,7 +8102,9 @@
       <c r="D31" s="12" t="n">
         <v>6000</v>
       </c>
-      <c r="E31" s="72"/>
+      <c r="E31" s="74" t="n">
+        <v>6000</v>
+      </c>
       <c r="F31" s="14"/>
     </row>
     <row r="32" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8064,7 +8120,7 @@
       <c r="D32" s="26" t="n">
         <v>6000</v>
       </c>
-      <c r="E32" s="76" t="n">
+      <c r="E32" s="78" t="n">
         <v>6000</v>
       </c>
       <c r="F32" s="27"/>
@@ -8082,7 +8138,7 @@
       <c r="D33" s="31" t="n">
         <v>6000</v>
       </c>
-      <c r="E33" s="77" t="n">
+      <c r="E33" s="79" t="n">
         <v>6000</v>
       </c>
       <c r="F33" s="20"/>
@@ -8100,7 +8156,7 @@
       <c r="D34" s="12" t="n">
         <v>6000</v>
       </c>
-      <c r="E34" s="72" t="n">
+      <c r="E34" s="74" t="n">
         <v>6000</v>
       </c>
       <c r="F34" s="14"/>
@@ -8111,18 +8167,18 @@
         <v>63</v>
       </c>
       <c r="C35" s="1"/>
-      <c r="D35" s="63" t="n">
+      <c r="D35" s="80" t="n">
         <f aca="false">SUM(D3:D34)</f>
         <v>173500</v>
       </c>
-      <c r="E35" s="78"/>
+      <c r="E35" s="81"/>
       <c r="F35" s="1"/>
     </row>
     <row r="36" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
-      <c r="E36" s="79"/>
+      <c r="E36" s="82"/>
       <c r="F36" s="1"/>
     </row>
     <row r="37" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8131,7 +8187,7 @@
         <v>64</v>
       </c>
       <c r="C37" s="36"/>
-      <c r="E37" s="71"/>
+      <c r="E37" s="73"/>
       <c r="F37" s="1"/>
     </row>
     <row r="38" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8147,7 +8203,7 @@
       <c r="D38" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E38" s="74" t="n">
+      <c r="E38" s="76" t="n">
         <v>5000</v>
       </c>
       <c r="F38" s="1"/>
@@ -8165,7 +8221,7 @@
       <c r="D39" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E39" s="74" t="n">
+      <c r="E39" s="76" t="n">
         <v>5000</v>
       </c>
       <c r="F39" s="1"/>
@@ -8183,7 +8239,7 @@
       <c r="D40" s="26" t="n">
         <v>5000</v>
       </c>
-      <c r="E40" s="80" t="n">
+      <c r="E40" s="83" t="n">
         <v>5000</v>
       </c>
       <c r="F40" s="1"/>
@@ -8201,7 +8257,7 @@
       <c r="D41" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E41" s="72" t="n">
+      <c r="E41" s="74" t="n">
         <v>5000</v>
       </c>
       <c r="F41" s="1"/>
@@ -8219,7 +8275,7 @@
       <c r="D42" s="18" t="n">
         <v>5000</v>
       </c>
-      <c r="E42" s="74" t="n">
+      <c r="E42" s="76" t="n">
         <v>5000</v>
       </c>
       <c r="F42" s="1"/>
@@ -8237,7 +8293,7 @@
       <c r="D43" s="40" t="n">
         <v>8500</v>
       </c>
-      <c r="E43" s="81" t="n">
+      <c r="E43" s="84" t="n">
         <v>8500</v>
       </c>
       <c r="F43" s="1"/>
@@ -8253,7 +8309,7 @@
       <c r="D44" s="45" t="n">
         <v>5000</v>
       </c>
-      <c r="E44" s="82" t="n">
+      <c r="E44" s="85" t="n">
         <v>5000</v>
       </c>
       <c r="F44" s="1"/>
@@ -8271,7 +8327,7 @@
       <c r="D45" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E45" s="72" t="n">
+      <c r="E45" s="74" t="n">
         <v>5000</v>
       </c>
       <c r="F45" s="1"/>
@@ -8289,7 +8345,7 @@
       <c r="D46" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E46" s="72" t="n">
+      <c r="E46" s="74" t="n">
         <v>5000</v>
       </c>
       <c r="F46" s="1"/>
@@ -8304,35 +8360,35 @@
         <f aca="false">SUM(D38:D46)</f>
         <v>48500</v>
       </c>
-      <c r="E47" s="83"/>
+      <c r="E47" s="86"/>
       <c r="F47" s="1"/>
     </row>
     <row r="48" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="9"/>
       <c r="B48" s="10"/>
       <c r="C48" s="11"/>
-      <c r="E48" s="74"/>
+      <c r="E48" s="76"/>
       <c r="F48" s="1"/>
     </row>
     <row r="49" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="23"/>
       <c r="B49" s="10"/>
       <c r="C49" s="11"/>
-      <c r="E49" s="74"/>
+      <c r="E49" s="76"/>
       <c r="F49" s="1"/>
     </row>
     <row r="50" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
-      <c r="E50" s="79"/>
+      <c r="E50" s="82"/>
       <c r="F50" s="1"/>
     </row>
     <row r="51" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
-      <c r="E51" s="79"/>
+      <c r="E51" s="82"/>
       <c r="F51" s="1"/>
     </row>
     <row r="52" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8341,7 +8397,7 @@
         <v>81</v>
       </c>
       <c r="C52" s="36"/>
-      <c r="E52" s="71"/>
+      <c r="E52" s="73"/>
       <c r="F52" s="1"/>
     </row>
     <row r="53" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8357,7 +8413,9 @@
       <c r="D53" s="12" t="n">
         <v>8500</v>
       </c>
-      <c r="E53" s="74"/>
+      <c r="E53" s="76" t="n">
+        <v>8500</v>
+      </c>
       <c r="F53" s="1"/>
     </row>
     <row r="54" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8373,7 +8431,7 @@
       <c r="D54" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E54" s="72" t="n">
+      <c r="E54" s="74" t="n">
         <v>5000</v>
       </c>
       <c r="F54" s="1"/>
@@ -8391,7 +8449,7 @@
       <c r="D55" s="18" t="n">
         <v>5000</v>
       </c>
-      <c r="E55" s="75" t="n">
+      <c r="E55" s="77" t="n">
         <v>5000</v>
       </c>
       <c r="F55" s="1"/>
@@ -8409,7 +8467,7 @@
       <c r="D56" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E56" s="74" t="n">
+      <c r="E56" s="76" t="n">
         <v>5000</v>
       </c>
       <c r="F56" s="1"/>
@@ -8427,7 +8485,7 @@
       <c r="D57" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E57" s="74" t="n">
+      <c r="E57" s="76" t="n">
         <v>5000</v>
       </c>
       <c r="F57" s="1"/>
@@ -8445,7 +8503,7 @@
       <c r="D58" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E58" s="72" t="n">
+      <c r="E58" s="74" t="n">
         <v>5000</v>
       </c>
       <c r="F58" s="1"/>
@@ -8463,7 +8521,9 @@
       <c r="D59" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E59" s="74"/>
+      <c r="E59" s="76" t="n">
+        <v>5000</v>
+      </c>
       <c r="F59" s="1"/>
     </row>
     <row r="60" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8477,10 +8537,10 @@
         <v>97</v>
       </c>
       <c r="D60" s="18" t="n">
-        <v>8500</v>
-      </c>
-      <c r="E60" s="73" t="n">
-        <v>8500</v>
+        <v>7500</v>
+      </c>
+      <c r="E60" s="75" t="n">
+        <v>7500</v>
       </c>
       <c r="F60" s="1"/>
     </row>
@@ -8492,23 +8552,23 @@
       <c r="C61" s="1"/>
       <c r="D61" s="50" t="n">
         <f aca="false">SUM(D53:D60)</f>
-        <v>47000</v>
-      </c>
-      <c r="E61" s="84"/>
+        <v>46000</v>
+      </c>
+      <c r="E61" s="87"/>
       <c r="F61" s="1"/>
     </row>
     <row r="62" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
-      <c r="E62" s="79"/>
+      <c r="E62" s="82"/>
       <c r="F62" s="1"/>
     </row>
     <row r="63" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
-      <c r="E63" s="79"/>
+      <c r="E63" s="82"/>
       <c r="F63" s="1"/>
     </row>
     <row r="64" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8517,7 +8577,7 @@
         <v>98</v>
       </c>
       <c r="C64" s="36"/>
-      <c r="E64" s="71"/>
+      <c r="E64" s="73"/>
       <c r="F64" s="1"/>
     </row>
     <row r="65" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8533,7 +8593,7 @@
       <c r="D65" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E65" s="74" t="n">
+      <c r="E65" s="76" t="n">
         <v>5000</v>
       </c>
       <c r="F65" s="1"/>
@@ -8551,7 +8611,7 @@
       <c r="D66" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E66" s="74" t="n">
+      <c r="E66" s="76" t="n">
         <v>5000</v>
       </c>
       <c r="F66" s="1"/>
@@ -8569,7 +8629,7 @@
       <c r="D67" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E67" s="72" t="n">
+      <c r="E67" s="74" t="n">
         <v>5000</v>
       </c>
       <c r="F67" s="1"/>
@@ -8587,7 +8647,9 @@
       <c r="D68" s="12" t="n">
         <v>8500</v>
       </c>
-      <c r="E68" s="74"/>
+      <c r="E68" s="76" t="n">
+        <v>8500</v>
+      </c>
       <c r="F68" s="1"/>
     </row>
     <row r="69" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8603,7 +8665,7 @@
       <c r="D69" s="12" t="n">
         <v>8500</v>
       </c>
-      <c r="E69" s="74" t="n">
+      <c r="E69" s="76" t="n">
         <v>8500</v>
       </c>
       <c r="F69" s="1"/>
@@ -8621,7 +8683,7 @@
       <c r="D70" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E70" s="72" t="n">
+      <c r="E70" s="74" t="n">
         <v>5000</v>
       </c>
       <c r="F70" s="1"/>
@@ -8631,15 +8693,13 @@
         <v>7</v>
       </c>
       <c r="B71" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="C71" s="11" t="s">
-        <v>112</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="C71" s="11"/>
       <c r="D71" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E71" s="72"/>
+      <c r="E71" s="74"/>
       <c r="F71" s="1"/>
     </row>
     <row r="72" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8655,7 +8715,9 @@
       <c r="D72" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E72" s="74"/>
+      <c r="E72" s="76" t="n">
+        <v>5000</v>
+      </c>
       <c r="F72" s="1"/>
     </row>
     <row r="73" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8671,7 +8733,7 @@
       <c r="D73" s="18" t="n">
         <v>5000</v>
       </c>
-      <c r="E73" s="73" t="n">
+      <c r="E73" s="75" t="n">
         <v>5000</v>
       </c>
       <c r="F73" s="1"/>
@@ -8689,7 +8751,7 @@
       <c r="D74" s="18" t="n">
         <v>5000</v>
       </c>
-      <c r="E74" s="75" t="n">
+      <c r="E74" s="77" t="n">
         <v>5000</v>
       </c>
       <c r="F74" s="1"/>
@@ -8707,7 +8769,7 @@
       <c r="D75" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E75" s="74" t="n">
+      <c r="E75" s="76" t="n">
         <v>5000</v>
       </c>
       <c r="F75" s="1"/>
@@ -8725,7 +8787,9 @@
       <c r="D76" s="26" t="n">
         <v>5000</v>
       </c>
-      <c r="E76" s="76"/>
+      <c r="E76" s="78" t="n">
+        <v>5000</v>
+      </c>
       <c r="F76" s="1"/>
     </row>
     <row r="77" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8741,7 +8805,7 @@
       <c r="D77" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E77" s="74" t="n">
+      <c r="E77" s="76" t="n">
         <v>5000</v>
       </c>
       <c r="F77" s="1"/>
@@ -8759,7 +8823,7 @@
       <c r="D78" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E78" s="74" t="n">
+      <c r="E78" s="76" t="n">
         <v>5000</v>
       </c>
       <c r="F78" s="1"/>
@@ -8768,12 +8832,12 @@
       <c r="A79" s="23" t="n">
         <v>15</v>
       </c>
-      <c r="B79" s="24" t="s">
-        <v>223</v>
-      </c>
+      <c r="B79" s="24"/>
       <c r="C79" s="25"/>
-      <c r="D79" s="26"/>
-      <c r="E79" s="76" t="n">
+      <c r="D79" s="26" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E79" s="78" t="n">
         <v>5000</v>
       </c>
       <c r="F79" s="1"/>
@@ -8787,7 +8851,7 @@
       <c r="D80" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="E80" s="71"/>
+      <c r="E80" s="73"/>
       <c r="F80" s="1"/>
     </row>
     <row r="81" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8803,7 +8867,7 @@
       <c r="D81" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E81" s="74" t="n">
+      <c r="E81" s="76" t="n">
         <v>5000</v>
       </c>
       <c r="F81" s="1"/>
@@ -8821,7 +8885,7 @@
       <c r="D82" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E82" s="72" t="n">
+      <c r="E82" s="74" t="n">
         <v>5000</v>
       </c>
       <c r="F82" s="1"/>
@@ -8839,7 +8903,9 @@
       <c r="D83" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E83" s="74"/>
+      <c r="E83" s="76" t="n">
+        <v>5000</v>
+      </c>
       <c r="F83" s="1"/>
     </row>
     <row r="84" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8855,7 +8921,7 @@
       <c r="D84" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E84" s="74" t="n">
+      <c r="E84" s="76" t="n">
         <v>5000</v>
       </c>
       <c r="F84" s="1"/>
@@ -8873,7 +8939,7 @@
       <c r="D85" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E85" s="72" t="n">
+      <c r="E85" s="74" t="n">
         <v>5000</v>
       </c>
       <c r="F85" s="1"/>
@@ -8891,7 +8957,7 @@
       <c r="D86" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="E86" s="74" t="n">
+      <c r="E86" s="76" t="n">
         <v>5000</v>
       </c>
       <c r="F86" s="1"/>
@@ -8904,23 +8970,23 @@
       <c r="C87" s="1"/>
       <c r="D87" s="51" t="n">
         <f aca="false">SUM(D65:D86)</f>
-        <v>107000</v>
-      </c>
-      <c r="E87" s="78"/>
+        <v>112000</v>
+      </c>
+      <c r="E87" s="81"/>
       <c r="F87" s="1"/>
     </row>
     <row r="88" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
-      <c r="E88" s="79"/>
+      <c r="E88" s="82"/>
       <c r="F88" s="1"/>
     </row>
     <row r="89" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
-      <c r="E89" s="79"/>
+      <c r="E89" s="82"/>
       <c r="F89" s="1"/>
     </row>
     <row r="90" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8929,7 +8995,7 @@
         <v>142</v>
       </c>
       <c r="C90" s="36"/>
-      <c r="E90" s="71"/>
+      <c r="E90" s="73"/>
       <c r="F90" s="1"/>
     </row>
     <row r="91" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8945,7 +9011,7 @@
       <c r="D91" s="12" t="n">
         <v>10000</v>
       </c>
-      <c r="E91" s="74" t="n">
+      <c r="E91" s="76" t="n">
         <v>10000</v>
       </c>
       <c r="F91" s="1"/>
@@ -8963,7 +9029,7 @@
       <c r="D92" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E92" s="74" t="n">
+      <c r="E92" s="76" t="n">
         <v>11000</v>
       </c>
       <c r="F92" s="1"/>
@@ -8981,7 +9047,7 @@
       <c r="D93" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E93" s="74" t="n">
+      <c r="E93" s="76" t="n">
         <v>11000</v>
       </c>
       <c r="F93" s="1"/>
@@ -8999,7 +9065,7 @@
       <c r="D94" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E94" s="72" t="n">
+      <c r="E94" s="74" t="n">
         <v>11000</v>
       </c>
       <c r="F94" s="1"/>
@@ -9017,7 +9083,7 @@
       <c r="D95" s="26" t="n">
         <v>11000</v>
       </c>
-      <c r="E95" s="80" t="n">
+      <c r="E95" s="83" t="n">
         <v>11000</v>
       </c>
       <c r="F95" s="1"/>
@@ -9027,7 +9093,7 @@
         <v>6</v>
       </c>
       <c r="B96" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C96" s="11" t="n">
         <v>796923935</v>
@@ -9035,7 +9101,7 @@
       <c r="D96" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E96" s="74" t="n">
+      <c r="E96" s="76" t="n">
         <v>11000</v>
       </c>
       <c r="F96" s="1"/>
@@ -9053,7 +9119,7 @@
       <c r="D97" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E97" s="72" t="n">
+      <c r="E97" s="74" t="n">
         <v>11000</v>
       </c>
       <c r="F97" s="1"/>
@@ -9071,7 +9137,7 @@
       <c r="D98" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E98" s="74" t="n">
+      <c r="E98" s="76" t="n">
         <v>11000</v>
       </c>
       <c r="F98" s="1"/>
@@ -9089,7 +9155,7 @@
       <c r="D99" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E99" s="72" t="n">
+      <c r="E99" s="74" t="n">
         <v>11000</v>
       </c>
       <c r="F99" s="1"/>
@@ -9107,7 +9173,7 @@
       <c r="D100" s="12" t="n">
         <v>13000</v>
       </c>
-      <c r="E100" s="74" t="n">
+      <c r="E100" s="76" t="n">
         <v>13000</v>
       </c>
       <c r="F100" s="1"/>
@@ -9125,7 +9191,7 @@
       <c r="D101" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E101" s="72" t="n">
+      <c r="E101" s="74" t="n">
         <v>11000</v>
       </c>
       <c r="F101" s="1"/>
@@ -9143,7 +9209,7 @@
       <c r="D102" s="53" t="n">
         <v>10000</v>
       </c>
-      <c r="E102" s="72" t="n">
+      <c r="E102" s="74" t="n">
         <v>10000</v>
       </c>
       <c r="F102" s="1"/>
@@ -9161,7 +9227,7 @@
       <c r="D103" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E103" s="74" t="n">
+      <c r="E103" s="76" t="n">
         <v>11000</v>
       </c>
       <c r="F103" s="1"/>
@@ -9179,7 +9245,7 @@
       <c r="D104" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E104" s="72" t="n">
+      <c r="E104" s="74" t="n">
         <v>11000</v>
       </c>
       <c r="F104" s="1"/>
@@ -9194,28 +9260,28 @@
         <f aca="false">SUM(D91:D104)</f>
         <v>154000</v>
       </c>
-      <c r="E105" s="78"/>
+      <c r="E105" s="81"/>
       <c r="F105" s="1"/>
     </row>
     <row r="106" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
-      <c r="E106" s="79"/>
+      <c r="E106" s="82"/>
       <c r="F106" s="1"/>
     </row>
     <row r="107" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
-      <c r="E107" s="79"/>
+      <c r="E107" s="82"/>
       <c r="F107" s="1"/>
     </row>
     <row r="108" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
-      <c r="E108" s="79"/>
+      <c r="E108" s="82"/>
       <c r="F108" s="1"/>
     </row>
     <row r="109" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9224,7 +9290,7 @@
         <v>168</v>
       </c>
       <c r="C109" s="36"/>
-      <c r="E109" s="71"/>
+      <c r="E109" s="73"/>
       <c r="F109" s="1"/>
     </row>
     <row r="110" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9240,7 +9306,7 @@
       <c r="D110" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E110" s="72" t="n">
+      <c r="E110" s="74" t="n">
         <v>11000</v>
       </c>
       <c r="F110" s="1"/>
@@ -9258,7 +9324,7 @@
       <c r="D111" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E111" s="85" t="n">
+      <c r="E111" s="74" t="n">
         <v>11000</v>
       </c>
       <c r="F111" s="1"/>
@@ -9276,7 +9342,7 @@
       <c r="D112" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E112" s="86" t="n">
+      <c r="E112" s="76" t="n">
         <v>11000</v>
       </c>
       <c r="F112" s="1"/>
@@ -9294,8 +9360,8 @@
       <c r="D113" s="12" t="n">
         <v>14000</v>
       </c>
-      <c r="E113" s="86" t="n">
-        <v>11000</v>
+      <c r="E113" s="76" t="n">
+        <v>14000</v>
       </c>
       <c r="F113" s="1"/>
     </row>
@@ -9312,7 +9378,7 @@
       <c r="D114" s="26" t="n">
         <v>11000</v>
       </c>
-      <c r="E114" s="87" t="n">
+      <c r="E114" s="78" t="n">
         <v>11000</v>
       </c>
       <c r="F114" s="1"/>
@@ -9330,7 +9396,7 @@
       <c r="D115" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E115" s="85" t="n">
+      <c r="E115" s="74" t="n">
         <v>11000</v>
       </c>
       <c r="F115" s="1"/>
@@ -9348,7 +9414,7 @@
       <c r="D116" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E116" s="86" t="n">
+      <c r="E116" s="76" t="n">
         <v>11000</v>
       </c>
       <c r="F116" s="1"/>
@@ -9366,7 +9432,7 @@
       <c r="D117" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E117" s="85" t="n">
+      <c r="E117" s="74" t="n">
         <v>11000</v>
       </c>
       <c r="F117" s="1"/>
@@ -9384,8 +9450,8 @@
       <c r="D118" s="18" t="n">
         <v>14000</v>
       </c>
-      <c r="E118" s="88" t="n">
-        <v>11000</v>
+      <c r="E118" s="77" t="n">
+        <v>14000</v>
       </c>
       <c r="F118" s="1"/>
     </row>
@@ -9402,7 +9468,9 @@
       <c r="D119" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E119" s="86"/>
+      <c r="E119" s="76" t="n">
+        <v>11000</v>
+      </c>
       <c r="F119" s="1"/>
     </row>
     <row r="120" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9418,7 +9486,7 @@
       <c r="D120" s="18" t="n">
         <v>11000</v>
       </c>
-      <c r="E120" s="89" t="n">
+      <c r="E120" s="75" t="n">
         <v>11000</v>
       </c>
       <c r="F120" s="1"/>
@@ -9436,7 +9504,7 @@
       <c r="D121" s="18" t="n">
         <v>11000</v>
       </c>
-      <c r="E121" s="73" t="n">
+      <c r="E121" s="75" t="n">
         <v>11000</v>
       </c>
       <c r="F121" s="1"/>
@@ -9454,7 +9522,9 @@
       <c r="D122" s="18" t="n">
         <v>11000</v>
       </c>
-      <c r="E122" s="89"/>
+      <c r="E122" s="75" t="n">
+        <v>11000</v>
+      </c>
       <c r="F122" s="1"/>
     </row>
     <row r="123" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9470,7 +9540,7 @@
       <c r="D123" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E123" s="85" t="n">
+      <c r="E123" s="74" t="n">
         <v>11000</v>
       </c>
       <c r="F123" s="55"/>
@@ -9480,7 +9550,7 @@
         <v>15</v>
       </c>
       <c r="B124" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C124" s="11" t="n">
         <v>740808927</v>
@@ -9488,7 +9558,7 @@
       <c r="D124" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E124" s="86" t="n">
+      <c r="E124" s="76" t="n">
         <v>11000</v>
       </c>
       <c r="F124" s="1"/>
@@ -9506,7 +9576,7 @@
       <c r="D125" s="12" t="n">
         <v>11000</v>
       </c>
-      <c r="E125" s="86" t="n">
+      <c r="E125" s="76" t="n">
         <v>11000</v>
       </c>
       <c r="F125" s="1"/>
@@ -9524,8 +9594,8 @@
       <c r="D126" s="12" t="n">
         <v>14000</v>
       </c>
-      <c r="E126" s="86" t="n">
-        <v>11000</v>
+      <c r="E126" s="76" t="n">
+        <v>14000</v>
       </c>
       <c r="F126" s="1"/>
     </row>
@@ -9542,7 +9612,7 @@
       <c r="D127" s="18" t="n">
         <v>11000</v>
       </c>
-      <c r="E127" s="88" t="n">
+      <c r="E127" s="77" t="n">
         <v>11000</v>
       </c>
       <c r="F127" s="1"/>
@@ -9560,7 +9630,7 @@
       <c r="D128" s="18" t="n">
         <v>11000</v>
       </c>
-      <c r="E128" s="88" t="n">
+      <c r="E128" s="77" t="n">
         <v>11000</v>
       </c>
       <c r="F128" s="1"/>
@@ -9578,7 +9648,7 @@
       <c r="D129" s="18" t="n">
         <v>11000</v>
       </c>
-      <c r="E129" s="89" t="n">
+      <c r="E129" s="75" t="n">
         <v>11000</v>
       </c>
       <c r="F129" s="1"/>
@@ -9596,8 +9666,8 @@
       <c r="D130" s="12" t="n">
         <v>16000</v>
       </c>
-      <c r="E130" s="85" t="n">
-        <v>11000</v>
+      <c r="E130" s="74" t="n">
+        <v>16000</v>
       </c>
       <c r="F130" s="1"/>
     </row>
@@ -9611,7 +9681,7 @@
         <f aca="false">SUM(D110:D130)</f>
         <v>245000</v>
       </c>
-      <c r="E131" s="90"/>
+      <c r="E131" s="88"/>
       <c r="F131" s="1"/>
     </row>
     <row r="132" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9628,56 +9698,56 @@
       <c r="E133" s="58"/>
       <c r="F133" s="58"/>
     </row>
-    <row r="134" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
-      <c r="C134" s="59" t="s">
+      <c r="C134" s="89" t="s">
         <v>211</v>
       </c>
       <c r="D134" s="69" t="n">
         <v>775000</v>
       </c>
-      <c r="E134" s="91" t="n">
-        <f aca="false">SUM(E4:E133)</f>
-        <v>654000</v>
-      </c>
-      <c r="F134" s="61"/>
-    </row>
-    <row r="135" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E134" s="90" t="n">
+        <f aca="false">SUM(E3:E132)</f>
+        <v>774000</v>
+      </c>
+      <c r="F134" s="91"/>
+    </row>
+    <row r="135" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
-      <c r="C135" s="59"/>
-      <c r="E135" s="61"/>
-      <c r="F135" s="61"/>
-    </row>
-    <row r="136" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C135" s="89"/>
+      <c r="E135" s="92"/>
+      <c r="F135" s="91"/>
+    </row>
+    <row r="136" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
-      <c r="C136" s="59" t="s">
+      <c r="C136" s="89" t="s">
         <v>212</v>
       </c>
-      <c r="E136" s="63" t="n">
-        <v>38750</v>
-      </c>
-      <c r="F136" s="61"/>
-    </row>
-    <row r="137" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E136" s="90" t="n">
+        <v>38700</v>
+      </c>
+      <c r="F136" s="91"/>
+    </row>
+    <row r="137" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
-      <c r="C137" s="59"/>
-      <c r="E137" s="61"/>
-      <c r="F137" s="61"/>
-    </row>
-    <row r="138" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C137" s="89"/>
+      <c r="E137" s="92"/>
+      <c r="F137" s="91"/>
+    </row>
+    <row r="138" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
-      <c r="C138" s="59" t="s">
+      <c r="C138" s="89" t="s">
         <v>213</v>
       </c>
-      <c r="E138" s="63" t="n">
-        <v>736250</v>
-      </c>
-      <c r="F138" s="61"/>
+      <c r="E138" s="90" t="n">
+        <v>735300</v>
+      </c>
+      <c r="F138" s="91"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
